--- a/Nucleus_Combustible.xlsx
+++ b/Nucleus_Combustible.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R150"/>
+  <dimension ref="A1:R152"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -560,7 +560,7 @@
         <v>10</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K4" t="str">
         <v>CM-20260903-00000217</v>
@@ -728,7 +728,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -757,49 +757,49 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="B7" t="str">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="C7" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D7" t="str">
-        <v>/api/evidencia/foto/7/comb-1787785535994/comb_0.jpg?v=1787785136</v>
+        <v>/api/evidencia/foto/7/comb-1788794114232/comb_0.jpg?v=1788794125</v>
       </c>
       <c r="E7" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-24 18:03</v>
+        <v>2026-08-28 10:14</v>
       </c>
       <c r="G7" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H7" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I7" t="str">
         <v>10</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K7" t="str">
-        <v>CM-20260825-00000273</v>
+        <v>CM -20260829-00000043</v>
       </c>
       <c r="L7" t="str">
-        <v>N014-00001524</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>013212533_IC_San_Clemente</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N7" t="str">
-        <v>N014-00001524</v>
+        <v>N014-00001570</v>
       </c>
       <c r="O7" t="str">
-        <v>ATENCION  CORTE DE ENERGIA 013212533_IC_San_Clemente</v>
+        <v/>
       </c>
       <c r="P7" t="str">
         <v>CHINCHA</v>
@@ -808,169 +808,169 @@
         <v>PROPIO</v>
       </c>
       <c r="R7" t="str">
-        <v/>
+        <v>hvargas</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="B8" t="str">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="C8" t="str">
-        <v>GL16COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D8" t="str">
-        <v>/api/evidencia/foto/7/comb-1788205048546/comb_0.jpg?v=1788205051</v>
+        <v>/api/evidencia/foto/7/166/comb_0.jpg?v=1788794407</v>
       </c>
       <c r="E8" t="str">
-        <v>MARCO ANTONIO SOTO BENIQUE</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-30 14:35</v>
+        <v>2026-09-07 10:18</v>
       </c>
       <c r="G8" t="str">
         <v>GASTO</v>
       </c>
       <c r="H8" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I8" t="str">
         <v>10</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K8" t="str">
-        <v>CM-20260830-00000074</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>RFC-20260830-0006</v>
+        <v>N014-00001570</v>
       </c>
       <c r="M8" t="str">
-        <v>0132801_PN_Jayllihuaya</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N8" t="str">
         <v/>
       </c>
       <c r="O8" t="str">
-        <v>N005-00001034 Se consume 10gl</v>
+        <v/>
       </c>
       <c r="P8" t="str">
-        <v>PUNO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q8" t="str">
         <v>PROPIO</v>
       </c>
       <c r="R8" t="str">
-        <v/>
+        <v>hvargas</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="B9" t="str">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="C9" t="str">
-        <v>GL12COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D9" t="str">
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>RAUL RIVERA TRUCIOS</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-30 15:54</v>
+        <v>2026-08-18 00:01</v>
       </c>
       <c r="G9" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H9" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I9" t="str">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K9" t="str">
-        <v>CM-20260823-00000077</v>
+        <v>CM-20260817-00000221</v>
       </c>
       <c r="L9" t="str">
-        <v>SE EMITE AL CIERRE</v>
+        <v/>
       </c>
       <c r="M9" t="str">
-        <v>0133945_JU_Mina_Ariana</v>
+        <v/>
       </c>
       <c r="N9" t="str">
-        <v>SE EMITE AL TERMINO</v>
+        <v/>
       </c>
       <c r="O9" t="str">
-        <v>FALTA EL CONSUO</v>
+        <v>DESPUES SE ESTARA SUBIENDO LA NOTA DE VENTA</v>
       </c>
       <c r="P9" t="str">
-        <v>HUANCAYO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q9" t="str">
         <v>PROPIO</v>
       </c>
       <c r="R9" t="str">
-        <v/>
+        <v>hvargas</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>57</v>
+      </c>
+      <c r="B10" t="str">
         <v>75</v>
       </c>
-      <c r="B10" t="str">
-        <v>78</v>
-      </c>
       <c r="C10" t="str">
-        <v>GL18COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787785535994/comb_0.jpg?v=1787785136</v>
       </c>
       <c r="E10" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-26 21:16</v>
+        <v>2026-08-24 18:03</v>
       </c>
       <c r="G10" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H10" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I10" t="str">
+        <v>10</v>
+      </c>
+      <c r="J10">
         <v>40</v>
       </c>
-      <c r="J10">
-        <v>45</v>
-      </c>
       <c r="K10" t="str">
-        <v/>
+        <v>CM-20260825-00000273</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>N014-00001524</v>
       </c>
       <c r="M10" t="str">
-        <v>varios</v>
+        <v>013212533_IC_San_Clemente</v>
       </c>
       <c r="N10" t="str">
-        <v>SE EMITE DESPUES DE CADA RETIRO</v>
+        <v>N014-00001524</v>
       </c>
       <c r="O10" t="str">
-        <v>CORTE PROGRAMADO EN VARISO SITES</v>
+        <v>ATENCION  CORTE DE ENERGIA 013212533_IC_San_Clemente</v>
       </c>
       <c r="P10" t="str">
-        <v>ICA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q10" t="str">
         <v>PROPIO</v>
@@ -981,52 +981,52 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="B11" t="str">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="C11" t="str">
-        <v>GL02COB</v>
+        <v>GL16COB</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1788205048546/comb_0.jpg?v=1788205051</v>
       </c>
       <c r="E11" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MARCO ANTONIO SOTO BENIQUE</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-26 11:16</v>
+        <v>2026-08-30 14:35</v>
       </c>
       <c r="G11" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H11" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I11" t="str">
         <v>10</v>
       </c>
       <c r="J11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K11" t="str">
-        <v>CM-20260826-00000215</v>
+        <v>CM-20260830-00000074</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>RFC-20260830-0006</v>
       </c>
       <c r="M11" t="str">
-        <v>BODEGA COW</v>
+        <v>0132801_PN_Jayllihuaya</v>
       </c>
       <c r="N11" t="str">
-        <v>SE EMITE DESPUES DE RETIRO</v>
+        <v/>
       </c>
       <c r="O11" t="str">
-        <v>ATENCION DE EMEREGCIA</v>
+        <v>N005-00001034 Se consume 10gl</v>
       </c>
       <c r="P11" t="str">
-        <v>CHINCHA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q11" t="str">
         <v>PROPIO</v>
@@ -1037,52 +1037,52 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B12" t="str">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="C12" t="str">
-        <v>GL16HWI</v>
+        <v>GL12COB</v>
       </c>
       <c r="D12" t="str">
-        <v>/api/evidencia/foto/7/comb-1787850765325/comb_0.jpg?v=1787850367</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>RAUL RIVERA TRUCIOS</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-26 12:11</v>
+        <v>2026-08-30 15:54</v>
       </c>
       <c r="G12" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H12" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I12" t="str">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J12">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K12" t="str">
-        <v>CM-20260826-00000206</v>
+        <v>CM-20260823-00000077</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>SE EMITE AL CIERRE</v>
       </c>
       <c r="M12" t="str">
-        <v>0130816_IC_Alto_Pisco</v>
+        <v>0133945_JU_Mina_Ariana</v>
       </c>
       <c r="N12" t="str">
-        <v>N014-00001557</v>
+        <v>SE EMITE AL TERMINO</v>
       </c>
       <c r="O12" t="str">
-        <v>ATENCION DE 0130816_IC_Alto_Pisco HIBRIDO</v>
+        <v>FALTA EL CONSUO</v>
       </c>
       <c r="P12" t="str">
-        <v>CHINCHA</v>
+        <v>HUANCAYO</v>
       </c>
       <c r="Q12" t="str">
         <v>PROPIO</v>
@@ -1093,52 +1093,52 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="B13" t="str">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="C13" t="str">
-        <v>GL16HWI</v>
+        <v>GL18COB</v>
       </c>
       <c r="D13" t="str">
-        <v>/api/evidencia/foto/7/comb-1788384821236/comb_0.jpg?v=1788384824</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-09-02 16:26</v>
+        <v>2026-08-26 21:16</v>
       </c>
       <c r="G13" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H13" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I13" t="str">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="J13">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="K13" t="str">
-        <v>CM-20260902-00000088</v>
+        <v/>
       </c>
       <c r="L13" t="str">
-        <v>RFC-2026902-0017</v>
+        <v/>
       </c>
       <c r="M13" t="str">
-        <v>0130816_IC_Alto_Pisco</v>
+        <v>varios</v>
       </c>
       <c r="N13" t="str">
-        <v>N014-00001612</v>
+        <v>SE EMITE DESPUES DE CADA RETIRO</v>
       </c>
       <c r="O13" t="str">
-        <v/>
+        <v>CORTE PROGRAMADO EN VARISO SITES</v>
       </c>
       <c r="P13" t="str">
-        <v>CHINCHA</v>
+        <v>ICA</v>
       </c>
       <c r="Q13" t="str">
         <v>PROPIO</v>
@@ -1149,49 +1149,49 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="B14" t="str">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="C14" t="str">
-        <v>GL16HWI</v>
+        <v>GL02COB</v>
       </c>
       <c r="D14" t="str">
-        <v>/api/evidencia/foto/7/comb-1788384983095/comb_0.jpg?v=1788384984</v>
+        <v/>
       </c>
       <c r="E14" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-09-02 16:34</v>
+        <v>2026-08-26 11:16</v>
       </c>
       <c r="G14" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H14" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I14" t="str">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K14" t="str">
-        <v>CM-202600902-00000088</v>
+        <v>CM-20260826-00000215</v>
       </c>
       <c r="L14" t="str">
-        <v>N014-00001612</v>
+        <v/>
       </c>
       <c r="M14" t="str">
-        <v>0130816_IC_Alto_Pisco</v>
+        <v>BODEGA COW</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>SE EMITE DESPUES DE RETIRO</v>
       </c>
       <c r="O14" t="str">
-        <v>RFC-2026902-0017</v>
+        <v>ATENCION DE EMEREGCIA</v>
       </c>
       <c r="P14" t="str">
         <v>CHINCHA</v>
@@ -1205,52 +1205,52 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B15" t="str">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C15" t="str">
-        <v>GL11COB</v>
+        <v>GL16HWI</v>
       </c>
       <c r="D15" t="str">
-        <v>/api/evidencia/foto/7/9/comb_0.jpg?v=1787256915</v>
+        <v>/api/evidencia/foto/7/comb-1787850765325/comb_0.jpg?v=1787850367</v>
       </c>
       <c r="E15" t="str">
-        <v>MARCO ANTONIO SOTO BENIQUE</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-18 00:00</v>
+        <v>2026-08-26 12:11</v>
       </c>
       <c r="G15" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H15" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I15" t="str">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="K15" t="str">
-        <v>CM-20260817-00000153</v>
+        <v>CM-20260826-00000206</v>
       </c>
       <c r="L15" t="str">
         <v/>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>0130816_IC_Alto_Pisco</v>
       </c>
       <c r="N15" t="str">
-        <v>N015-00000912</v>
+        <v>N014-00001557</v>
       </c>
       <c r="O15" t="str">
-        <v>:013310225_PN_Coasa falta boleta</v>
+        <v>ATENCION DE 0130816_IC_Alto_Pisco HIBRIDO</v>
       </c>
       <c r="P15" t="str">
-        <v>PUNO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q15" t="str">
         <v>PROPIO</v>
@@ -1261,52 +1261,52 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="B16" t="str">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="C16" t="str">
-        <v>GL11COB</v>
+        <v>GL16HWI</v>
       </c>
       <c r="D16" t="str">
-        <v>/api/evidencia/foto/7/comb-1787608424204/comb_0.jpg?v=1787608425</v>
+        <v>/api/evidencia/foto/7/comb-1788384821236/comb_0.jpg?v=1788384824</v>
       </c>
       <c r="E16" t="str">
-        <v>DINO ANTHONY QUISPE FLORES</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-09-02 16:26</v>
       </c>
       <c r="G16" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H16" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I16" t="str">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="J16">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K16" t="str">
-        <v>CM-20260821-00000051</v>
+        <v>CM-20260902-00000088</v>
       </c>
       <c r="L16" t="str">
-        <v>RFC-20260821-0021</v>
+        <v>RFC-2026902-0017</v>
       </c>
       <c r="M16" t="str">
-        <v>0132858_PN_Ananea</v>
+        <v>0130816_IC_Alto_Pisco</v>
       </c>
       <c r="N16" t="str">
-        <v>N014-00000901</v>
+        <v>N014-00001612</v>
       </c>
       <c r="O16" t="str">
-        <v>0132860_PN_El_Dorado_Puno  N014-00000901 qr de chirinos uso quispe flores 10gl</v>
+        <v/>
       </c>
       <c r="P16" t="str">
-        <v>PUNO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q16" t="str">
         <v>PROPIO</v>
@@ -1317,52 +1317,52 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B17" t="str">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C17" t="str">
-        <v>GL18COB</v>
+        <v>GL16HWI</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1788384983095/comb_0.jpg?v=1788384984</v>
       </c>
       <c r="E17" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-31 14:51</v>
+        <v>2026-09-02 16:34</v>
       </c>
       <c r="G17" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H17" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I17" t="str">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="J17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K17" t="str">
-        <v>CM-20260830-00005042</v>
+        <v>CM-202600902-00000088</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>N014-00001612</v>
       </c>
       <c r="M17" t="str">
-        <v>0130840_IC_Rep_Marcona</v>
+        <v>0130816_IC_Alto_Pisco</v>
       </c>
       <c r="N17" t="str">
-        <v>SE EMITE DESPUES DE RETIRO</v>
+        <v/>
       </c>
       <c r="O17" t="str">
-        <v>SE SOLICITO 5 GLS DE GASOLINA REGULAR</v>
+        <v>RFC-2026902-0017</v>
       </c>
       <c r="P17" t="str">
-        <v>ICA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q17" t="str">
         <v>PROPIO</v>
@@ -1373,52 +1373,52 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="B18" t="str">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="C18" t="str">
-        <v>GL02COB</v>
+        <v>GL11COB</v>
       </c>
       <c r="D18" t="str">
-        <v>/api/evidencia/foto/7/comb-1787855958993/comb_0.jpg?v=1787855956</v>
+        <v>/api/evidencia/foto/7/9/comb_0.jpg?v=1787256915</v>
       </c>
       <c r="E18" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MARCO ANTONIO SOTO BENIQUE</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-27 13:33</v>
+        <v>2026-08-18 00:00</v>
       </c>
       <c r="G18" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H18" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I18" t="str">
         <v>10</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K18" t="str">
-        <v>CM -20260826-00000215</v>
+        <v>CM-20260817-00000153</v>
       </c>
       <c r="L18" t="str">
-        <v>N014-00001553</v>
+        <v/>
       </c>
       <c r="M18" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v/>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>N015-00000912</v>
       </c>
       <c r="O18" t="str">
-        <v>SE REALIZA RENDICION DE 10 GLNS RETIRADOS PARA ATENCION DE  CM -20260826-00000215  PARA EL SITE IC_BODEGA_COW</v>
+        <v>:013310225_PN_Coasa falta boleta</v>
       </c>
       <c r="P18" t="str">
-        <v>CHINCHA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q18" t="str">
         <v>PROPIO</v>
@@ -1429,52 +1429,52 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B19" t="str">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="C19" t="str">
-        <v>GL16HWI</v>
+        <v>GL11COB</v>
       </c>
       <c r="D19" t="str">
-        <v>/api/evidencia/foto/7/comb-1787864230679/comb_0.jpg?v=1787864224</v>
+        <v>/api/evidencia/foto/7/comb-1787608424204/comb_0.jpg?v=1787608425</v>
       </c>
       <c r="E19" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>DINO ANTHONY QUISPE FLORES</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-27 15:51</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G19" t="str">
         <v>GASTO</v>
       </c>
       <c r="H19" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I19" t="str">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K19" t="str">
-        <v>CM-20260826-00000206</v>
+        <v>CM-20260821-00000051</v>
       </c>
       <c r="L19" t="str">
-        <v>CM-20260826-00000206</v>
+        <v>RFC-20260821-0021</v>
       </c>
       <c r="M19" t="str">
-        <v>0130816_IC_Alto_Pisco</v>
+        <v>0132858_PN_Ananea</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>N014-00000901</v>
       </c>
       <c r="O19" t="str">
-        <v>SE RINDE RETIRO DE 200 GLNS PARA ATENCION DE CM-20260826-00000206 PARA EL SITE IC_ALTO_PISCO</v>
+        <v>0132860_PN_El_Dorado_Puno  N014-00000901 qr de chirinos uso quispe flores 10gl</v>
       </c>
       <c r="P19" t="str">
-        <v>CHINCHA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q19" t="str">
         <v>PROPIO</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B20" t="str">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C20" t="str">
         <v>GL18COB</v>
@@ -1500,10 +1500,10 @@
         <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-31 14:59</v>
+        <v>2026-08-31 14:51</v>
       </c>
       <c r="G20" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H20" t="str">
         <v>lgutierrez</v>
@@ -1512,22 +1512,22 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K20" t="str">
-        <v>CM-20260830-00000265</v>
+        <v>CM-20260830-00005042</v>
       </c>
       <c r="L20" t="str">
-        <v>N15-00001651</v>
+        <v/>
       </c>
       <c r="M20" t="str">
-        <v>0134672_IC_Avenida_Siete</v>
+        <v>0130840_IC_Rep_Marcona</v>
       </c>
       <c r="N20" t="str">
-        <v>N15-00001651</v>
+        <v>SE EMITE DESPUES DE RETIRO</v>
       </c>
       <c r="O20" t="str">
-        <v>SE ABASTECION 5 GLS AL SITE RETIRADO 31.08</v>
+        <v>SE SOLICITO 5 GLS DE GASOLINA REGULAR</v>
       </c>
       <c r="P20" t="str">
         <v>ICA</v>
@@ -1541,52 +1541,52 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B21" t="str">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C21" t="str">
-        <v>GL18COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D21" t="str">
-        <v>/api/evidencia/foto/7/comb-1787678241132/comb_0.jpg?v=1787677841</v>
+        <v>/api/evidencia/foto/7/comb-1787855958993/comb_0.jpg?v=1787855956</v>
       </c>
       <c r="E21" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-27 13:33</v>
       </c>
       <c r="G21" t="str">
         <v>GASTO</v>
       </c>
       <c r="H21" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I21" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K21" t="str">
-        <v>CM-20260823-00000397</v>
+        <v>CM -20260826-00000215</v>
       </c>
       <c r="L21" t="str">
-        <v>N024-00002843</v>
+        <v>N014-00001553</v>
       </c>
       <c r="M21" t="str">
-        <v>SITE 0132581_IC_Juan_Quinones</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N21" t="str">
-        <v>N024-00002843</v>
+        <v/>
       </c>
       <c r="O21" t="str">
-        <v>ATENCION CORTE PROGRAMADO SITE 0132581_IC_Juan_Quinones</v>
+        <v>SE REALIZA RENDICION DE 10 GLNS RETIRADOS PARA ATENCION DE  CM -20260826-00000215  PARA EL SITE IC_BODEGA_COW</v>
       </c>
       <c r="P21" t="str">
-        <v>ICA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q21" t="str">
         <v>PROPIO</v>
@@ -1597,52 +1597,52 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B22" t="str">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="C22" t="str">
-        <v>GL17COB</v>
+        <v>GL16HWI</v>
       </c>
       <c r="D22" t="str">
-        <v>/api/evidencia/foto/7/comb-1787678771260/comb_0.jpg?v=1787678777</v>
+        <v>/api/evidencia/foto/7/comb-1787864230679/comb_0.jpg?v=1787864224</v>
       </c>
       <c r="E22" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-25 00:00</v>
+        <v>2026-08-27 15:51</v>
       </c>
       <c r="G22" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H22" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I22" t="str">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="J22">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K22" t="str">
-        <v>CM-20260825-00000114</v>
+        <v>CM-20260826-00000206</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>CM-20260826-00000206</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>0130816_IC_Alto_Pisco</v>
       </c>
       <c r="N22" t="str">
-        <v>N029-00001224</v>
+        <v/>
       </c>
       <c r="O22" t="str">
-        <v>013141788_AQ_RosarioApipa N029-00001224 10GL</v>
+        <v>SE RINDE RETIRO DE 200 GLNS PARA ATENCION DE CM-20260826-00000206 PARA EL SITE IC_ALTO_PISCO</v>
       </c>
       <c r="P22" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q22" t="str">
         <v>PROPIO</v>
@@ -1653,52 +1653,52 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="B23" t="str">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="C23" t="str">
-        <v>GL02COB</v>
+        <v>GL18COB</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-25 00:00</v>
+        <v>2026-08-31 14:59</v>
       </c>
       <c r="G23" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H23" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I23" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K23" t="str">
-        <v>CM-20260825-00000050</v>
+        <v>CM-20260830-00000265</v>
       </c>
       <c r="L23" t="str">
-        <v>SE EMITE CUANDO SE HAGA EL RETIRO</v>
+        <v>N15-00001651</v>
       </c>
       <c r="M23" t="str">
-        <v>BODEGA COW</v>
+        <v>0134672_IC_Avenida_Siete</v>
       </c>
       <c r="N23" t="str">
-        <v>SE EMITE UNA VEZ SE HAGA RETIRO</v>
+        <v>N15-00001651</v>
       </c>
       <c r="O23" t="str">
-        <v/>
+        <v>SE ABASTECION 5 GLS AL SITE RETIRADO 31.08</v>
       </c>
       <c r="P23" t="str">
-        <v>CHINCHA</v>
+        <v>ICA</v>
       </c>
       <c r="Q23" t="str">
         <v>PROPIO</v>
@@ -1709,52 +1709,52 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B24" t="str">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C24" t="str">
-        <v>GL04COB</v>
+        <v>GL18COB</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787678241132/comb_0.jpg?v=1787677841</v>
       </c>
       <c r="E24" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-19 00:00</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G24" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H24" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I24" t="str">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K24" t="str">
-        <v>CM-20260818-00000215</v>
+        <v>CM-20260823-00000397</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>N024-00002843</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>SITE 0132581_IC_Juan_Quinones</v>
       </c>
       <c r="N24" t="str">
-        <v>SE EMITE DEESPUES DE CADA RETIRO</v>
+        <v>N024-00002843</v>
       </c>
       <c r="O24" t="str">
-        <v>0133760_AY_Quinua</v>
+        <v>ATENCION CORTE PROGRAMADO SITE 0132581_IC_Juan_Quinones</v>
       </c>
       <c r="P24" t="str">
-        <v>AYACUCHO</v>
+        <v>ICA</v>
       </c>
       <c r="Q24" t="str">
         <v>PROPIO</v>
@@ -1765,37 +1765,37 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B25" t="str">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C25" t="str">
-        <v>GL24COB</v>
+        <v>GL17COB</v>
       </c>
       <c r="D25" t="str">
-        <v>/api/evidencia/foto/7/comb-1787170460611/comb_0.jpg?v=1787170462</v>
+        <v>/api/evidencia/foto/7/comb-1787678771260/comb_0.jpg?v=1787678777</v>
       </c>
       <c r="E25" t="str">
-        <v>YOVANIE ENRIQUEZ CASTILLO</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-19 00:00</v>
+        <v>2026-08-25 00:00</v>
       </c>
       <c r="G25" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H25" t="str">
         <v>ygalvez</v>
       </c>
       <c r="I25" t="str">
-        <v>0.75</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>9.25</v>
+        <v>18</v>
       </c>
       <c r="K25" t="str">
-        <v>CM-20260818-00000027</v>
+        <v>CM-20260825-00000114</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1804,13 +1804,13 @@
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>N574-00037928</v>
+        <v>N029-00001224</v>
       </c>
       <c r="O25" t="str">
-        <v>RFC-20260818-0041 SOLO SE CONSUME 0.75, SE RETIRA 10GL QUEDAN EN QR 10GL BOLETA N574-00037928</v>
+        <v>013141788_AQ_RosarioApipa N029-00001224 10GL</v>
       </c>
       <c r="P25" t="str">
-        <v>CUZCO</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q25" t="str">
         <v>PROPIO</v>
@@ -1821,52 +1821,52 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="B26" t="str">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="C26" t="str">
-        <v>GL06HWI</v>
+        <v>GL02COB</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>YON ROJAS TONCONI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-09-02 13:01</v>
+        <v>2026-08-25 00:00</v>
       </c>
       <c r="G26" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H26" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I26" t="str">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="K26" t="str">
-        <v>CM-20260824-00000046</v>
+        <v>CM-20260825-00000050</v>
       </c>
       <c r="L26" t="str">
-        <v>SE ADJUNTA AL CIERRE DE LA FAENA</v>
+        <v>SE EMITE CUANDO SE HAGA EL RETIRO</v>
       </c>
       <c r="M26" t="str">
-        <v>0131103_MQ_Cruz_del_Portillo</v>
+        <v>BODEGA COW</v>
       </c>
       <c r="N26" t="str">
-        <v>SE ADJUNTA AL CIERRE DE LA FAENA</v>
+        <v>SE EMITE UNA VEZ SE HAGA RETIRO</v>
       </c>
       <c r="O26" t="str">
-        <v>SE ADJUNTA AL CIERRE DE LA FAENA</v>
+        <v/>
       </c>
       <c r="P26" t="str">
-        <v>MOQUEGUA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q26" t="str">
         <v>PROPIO</v>
@@ -1877,52 +1877,52 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="B27" t="str">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="C27" t="str">
-        <v>GL06HWI</v>
+        <v>GL04COB</v>
       </c>
       <c r="D27" t="str">
-        <v>/api/evidencia/foto/7/comb-1788372669810/comb_0.jpg?v=1788372671</v>
+        <v/>
       </c>
       <c r="E27" t="str">
-        <v>YON ROJAS TONCONI</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-09-02 13:04</v>
+        <v>2026-08-19 00:00</v>
       </c>
       <c r="G27" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H27" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I27" t="str">
-        <v>92.200</v>
+        <v>16</v>
       </c>
       <c r="J27">
-        <v>407.8</v>
+        <v>16</v>
       </c>
       <c r="K27" t="str">
-        <v>CM-20260824-00000046</v>
+        <v>CM-20260818-00000215</v>
       </c>
       <c r="L27" t="str">
-        <v>NO20-00003476</v>
+        <v/>
       </c>
       <c r="M27" t="str">
-        <v>0131103_MQ_Cruz_del_Portillo</v>
+        <v/>
       </c>
       <c r="N27" t="str">
-        <v/>
+        <v>SE EMITE DEESPUES DE CADA RETIRO</v>
       </c>
       <c r="O27" t="str">
-        <v>NO20-00003476</v>
+        <v>0133760_AY_Quinua</v>
       </c>
       <c r="P27" t="str">
-        <v>MOQUEGUA</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q27" t="str">
         <v>PROPIO</v>
@@ -1933,52 +1933,52 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>131</v>
+        <v>12</v>
       </c>
       <c r="B28" t="str">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="C28" t="str">
-        <v>GL06HWI</v>
+        <v>GL24COB</v>
       </c>
       <c r="D28" t="str">
-        <v>/api/evidencia/foto/7/comb-1788372830444/comb_0.jpg?v=1788372832</v>
+        <v>/api/evidencia/foto/7/comb-1787170460611/comb_0.jpg?v=1787170462</v>
       </c>
       <c r="E28" t="str">
-        <v>YON ROJAS TONCONI</v>
+        <v>YOVANIE ENRIQUEZ CASTILLO</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-09-02 13:12</v>
+        <v>2026-08-19 00:00</v>
       </c>
       <c r="G28" t="str">
         <v>GASTO</v>
       </c>
       <c r="H28" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I28" t="str">
-        <v>407.8</v>
+        <v>0.75</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="K28" t="str">
-        <v>CM-20260824-00000046</v>
+        <v>CM-20260818-00000027</v>
       </c>
       <c r="L28" t="str">
-        <v>NO17-00003337</v>
+        <v/>
       </c>
       <c r="M28" t="str">
-        <v>0131103_MQ_Cruz_del_Portillo</v>
+        <v/>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>N574-00037928</v>
       </c>
       <c r="O28" t="str">
-        <v>NO17-00003337</v>
+        <v>RFC-20260818-0041 SOLO SE CONSUME 0.75, SE RETIRA 10GL QUEDAN EN QR 10GL BOLETA N574-00037928</v>
       </c>
       <c r="P28" t="str">
-        <v>MOQUEGUA</v>
+        <v>CUZCO</v>
       </c>
       <c r="Q28" t="str">
         <v>PROPIO</v>
@@ -1989,52 +1989,52 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="B29" t="str">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="C29" t="str">
-        <v>GL02COB</v>
+        <v>GL06HWI</v>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>YON ROJAS TONCONI</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-09-02 13:01</v>
       </c>
       <c r="G29" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H29" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I29" t="str">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="J29">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="K29" t="str">
-        <v>CM-20260820-00000060</v>
+        <v>CM-20260824-00000046</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>SE ADJUNTA AL CIERRE DE LA FAENA</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>0131103_MQ_Cruz_del_Portillo</v>
       </c>
       <c r="N29" t="str">
-        <v>PENDIENTE</v>
+        <v>SE ADJUNTA AL CIERRE DE LA FAENA</v>
       </c>
       <c r="O29" t="str">
-        <v>SITE BODEGA COW</v>
+        <v>SE ADJUNTA AL CIERRE DE LA FAENA</v>
       </c>
       <c r="P29" t="str">
-        <v>CHINCHA</v>
+        <v>MOQUEGUA</v>
       </c>
       <c r="Q29" t="str">
         <v>PROPIO</v>
@@ -2045,52 +2045,52 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="B30" t="str">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="C30" t="str">
-        <v>GL02COB</v>
+        <v>GL06HWI</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1788372669810/comb_0.jpg?v=1788372671</v>
       </c>
       <c r="E30" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>YON ROJAS TONCONI</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-09-02 13:04</v>
       </c>
       <c r="G30" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H30" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I30" t="str">
-        <v>10</v>
+        <v>92.200</v>
       </c>
       <c r="J30">
-        <v>30</v>
+        <v>407.8</v>
       </c>
       <c r="K30" t="str">
-        <v>CM-20260820-00000060</v>
+        <v>CM-20260824-00000046</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>NO20-00003476</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>0131103_MQ_Cruz_del_Portillo</v>
       </c>
       <c r="N30" t="str">
-        <v>PENDIENTE</v>
+        <v/>
       </c>
       <c r="O30" t="str">
-        <v>SITE BODEGA COW</v>
+        <v>NO20-00003476</v>
       </c>
       <c r="P30" t="str">
-        <v>CHINCHA</v>
+        <v>MOQUEGUA</v>
       </c>
       <c r="Q30" t="str">
         <v>PROPIO</v>
@@ -2101,52 +2101,52 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="B31" t="str">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="C31" t="str">
-        <v>GL02COB</v>
+        <v>GL06HWI</v>
       </c>
       <c r="D31" t="str">
-        <v>/api/evidencia/foto/7/comb-1787270638898/comb_0.jpg?v=1787270244</v>
+        <v>/api/evidencia/foto/7/comb-1788372830444/comb_0.jpg?v=1788372832</v>
       </c>
       <c r="E31" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>YON ROJAS TONCONI</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-20 00:00</v>
+        <v>2026-09-02 13:12</v>
       </c>
       <c r="G31" t="str">
         <v>GASTO</v>
       </c>
       <c r="H31" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I31" t="str">
-        <v>10</v>
+        <v>407.8</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="str">
-        <v>CM-20260820-00000060</v>
+        <v>CM-20260824-00000046</v>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>NO17-00003337</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>0131103_MQ_Cruz_del_Portillo</v>
       </c>
       <c r="N31" t="str">
         <v/>
       </c>
       <c r="O31" t="str">
-        <v>0133243 SITE IC_BODEGA</v>
+        <v>NO17-00003337</v>
       </c>
       <c r="P31" t="str">
-        <v>CHINCHA</v>
+        <v>MOQUEGUA</v>
       </c>
       <c r="Q31" t="str">
         <v>PROPIO</v>
@@ -2157,37 +2157,37 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B32" t="str">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C32" t="str">
-        <v>GL23COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D32" t="str">
-        <v>/api/evidencia/foto/7/6/comb_0.jpg?v=1787152864</v>
+        <v/>
       </c>
       <c r="E32" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-18 00:00</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G32" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H32" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I32" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K32" t="str">
-        <v>CM-20260818-00000097</v>
+        <v>CM-20260820-00000060</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -2196,13 +2196,13 @@
         <v/>
       </c>
       <c r="N32" t="str">
-        <v>N020-00003344</v>
+        <v>PENDIENTE</v>
       </c>
       <c r="O32" t="str">
-        <v>Site: 0134041_aq_sta_rita de siguas pendiente factura</v>
+        <v>SITE BODEGA COW</v>
       </c>
       <c r="P32" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q32" t="str">
         <v>PROPIO</v>
@@ -2213,52 +2213,52 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="B33" t="str">
-        <v>123</v>
+        <v>34</v>
       </c>
       <c r="C33" t="str">
-        <v>GL10COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D33" t="str">
-        <v>/api/evidencia/foto/7/comb-1788221490584/comb_0.jpg?v=1788221492</v>
+        <v/>
       </c>
       <c r="E33" t="str">
-        <v>ANDERSON CALANI HUILLCA</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-31 18:39</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G33" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H33" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I33" t="str">
-        <v>17.57</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>17.57</v>
+        <v>30</v>
       </c>
       <c r="K33" t="str">
-        <v>CM-20260829-00000340</v>
+        <v>CM-20260820-00000060</v>
       </c>
       <c r="L33" t="str">
-        <v>RFC-20260829-00002</v>
+        <v/>
       </c>
       <c r="M33" t="str">
-        <v>0132540_MD_Huepetuhe</v>
+        <v/>
       </c>
       <c r="N33" t="str">
-        <v>RFC-20260829-00002</v>
+        <v>PENDIENTE</v>
       </c>
       <c r="O33" t="str">
-        <v>SE</v>
+        <v>SITE BODEGA COW</v>
       </c>
       <c r="P33" t="str">
-        <v>PUERTO MALDONADO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q33" t="str">
         <v>PROPIO</v>
@@ -2269,52 +2269,52 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="B34" t="str">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="C34" t="str">
-        <v>GL10COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D34" t="str">
-        <v>/api/evidencia/foto/7/comb-1788221639704/comb_0.jpg?v=1788221642</v>
+        <v>/api/evidencia/foto/7/comb-1787270638898/comb_0.jpg?v=1787270244</v>
       </c>
       <c r="E34" t="str">
-        <v>ANDERSON CALANI HUILLCA</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-31 19:12</v>
+        <v>2026-08-20 00:00</v>
       </c>
       <c r="G34" t="str">
         <v>GASTO</v>
       </c>
       <c r="H34" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I34" t="str">
-        <v>17.57</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="str">
-        <v>CM-20260829-00000340</v>
+        <v>CM-20260820-00000060</v>
       </c>
       <c r="L34" t="str">
-        <v>CM-20260829-00000340</v>
+        <v/>
       </c>
       <c r="M34" t="str">
-        <v>0132537_MD_Caserio_Sta_Rosa</v>
+        <v/>
       </c>
       <c r="N34" t="str">
         <v/>
       </c>
       <c r="O34" t="str">
-        <v>CM-20260829-00000340</v>
+        <v>0133243 SITE IC_BODEGA</v>
       </c>
       <c r="P34" t="str">
-        <v>PUERTO MALDONADO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q34" t="str">
         <v>PROPIO</v>
@@ -2325,37 +2325,37 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B35" t="str">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C35" t="str">
-        <v>GL02COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D35" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/6/comb_0.jpg?v=1787152864</v>
       </c>
       <c r="E35" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-20 00:00</v>
+        <v>2026-08-18 00:00</v>
       </c>
       <c r="G35" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H35" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I35" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K35" t="str">
-        <v>CM-20260820-00000060</v>
+        <v>CM-20260818-00000097</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -2364,13 +2364,13 @@
         <v/>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>N020-00003344</v>
       </c>
       <c r="O35" t="str">
-        <v>se emite despues del pedido</v>
+        <v>Site: 0134041_aq_sta_rita de siguas pendiente factura</v>
       </c>
       <c r="P35" t="str">
-        <v>CHINCHA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q35" t="str">
         <v>PROPIO</v>
@@ -2381,52 +2381,52 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="B36" t="str">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="C36" t="str">
-        <v>GL17COB</v>
+        <v>GL10COB</v>
       </c>
       <c r="D36" t="str">
-        <v>/api/evidencia/foto/7/comb-1787784167343/comb_0.jpg?v=1787784173</v>
+        <v>/api/evidencia/foto/7/comb-1788221490584/comb_0.jpg?v=1788221492</v>
       </c>
       <c r="E36" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>ANDERSON CALANI HUILLCA</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-26 00:00</v>
+        <v>2026-08-31 18:39</v>
       </c>
       <c r="G36" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H36" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I36" t="str">
-        <v>10</v>
+        <v>17.57</v>
       </c>
       <c r="J36">
-        <v>8</v>
+        <v>17.57</v>
       </c>
       <c r="K36" t="str">
-        <v>CM-20260826-00000055</v>
+        <v>CM-20260829-00000340</v>
       </c>
       <c r="L36" t="str">
-        <v>RFC-20260826-0006</v>
+        <v>RFC-20260829-00002</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>0132540_MD_Huepetuhe</v>
       </c>
       <c r="N36" t="str">
-        <v/>
+        <v>RFC-20260829-00002</v>
       </c>
       <c r="O36" t="str">
-        <v>Se utiliza 5 galones pendientes de N029-00001224 Y 5 g 0134003_AQ_Sarcasalones que se retiro N029-00001232, en Total 10 glns de faena</v>
+        <v>SE</v>
       </c>
       <c r="P36" t="str">
-        <v>AREQUIPA</v>
+        <v>PUERTO MALDONADO</v>
       </c>
       <c r="Q36" t="str">
         <v>PROPIO</v>
@@ -2437,52 +2437,52 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="B37" t="str">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="C37" t="str">
-        <v>GL07COB</v>
+        <v>GL10COB</v>
       </c>
       <c r="D37" t="str">
-        <v>/api/evidencia/foto/7/comb-1787610099079/comb_0.jpg?v=1787610100</v>
+        <v>/api/evidencia/foto/7/comb-1788221639704/comb_0.jpg?v=1788221642</v>
       </c>
       <c r="E37" t="str">
-        <v>JOSE MIGUEL NINA ESQUIA</v>
+        <v>ANDERSON CALANI HUILLCA</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-08-31 19:12</v>
       </c>
       <c r="G37" t="str">
         <v>GASTO</v>
       </c>
       <c r="H37" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I37" t="str">
-        <v>4</v>
+        <v>17.57</v>
       </c>
       <c r="J37">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K37" t="str">
-        <v>CM-20260823-00000133</v>
+        <v>CM-20260829-00000340</v>
       </c>
       <c r="L37" t="str">
-        <v>RFC-20260823-0021</v>
+        <v>CM-20260829-00000340</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>0132537_MD_Caserio_Sta_Rosa</v>
       </c>
       <c r="N37" t="str">
         <v/>
       </c>
       <c r="O37" t="str">
-        <v>N034-00000377  0131298_TA_Boca_del_Rio se comsume 4gl</v>
+        <v>CM-20260829-00000340</v>
       </c>
       <c r="P37" t="str">
-        <v>TACNA</v>
+        <v>PUERTO MALDONADO</v>
       </c>
       <c r="Q37" t="str">
         <v>PROPIO</v>
@@ -2493,25 +2493,25 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="B38" t="str">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C38" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D38" t="str">
-        <v>/api/evidencia/foto/7/comb-1787611806002/comb_0.jpg?v=1787611407</v>
+        <v/>
       </c>
       <c r="E38" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-20 00:00</v>
       </c>
       <c r="G38" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H38" t="str">
         <v>lgutierrez</v>
@@ -2520,22 +2520,22 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K38" t="str">
-        <v>CM-20260822-00000057</v>
+        <v>CM-20260820-00000060</v>
       </c>
       <c r="L38" t="str">
-        <v>SITE 0133243 _IC_ BOGEGA_COW</v>
+        <v/>
       </c>
       <c r="M38" t="str">
-        <v>SITE 0133243 _IC_ BOGEGA_COW</v>
+        <v/>
       </c>
       <c r="N38" t="str">
-        <v>N024-00002836</v>
+        <v/>
       </c>
       <c r="O38" t="str">
-        <v>SITE 0133243 _IC_ BOGEGA_COW</v>
+        <v>se emite despues del pedido</v>
       </c>
       <c r="P38" t="str">
         <v>CHINCHA</v>
@@ -2549,52 +2549,52 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="B39" t="str">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="C39" t="str">
-        <v>GL02COB</v>
+        <v>GL17COB</v>
       </c>
       <c r="D39" t="str">
-        <v>/api/evidencia/foto/7/comb-1788394180486/comb_0.jpg?v=1788394185</v>
+        <v>/api/evidencia/foto/7/comb-1787784167343/comb_0.jpg?v=1787784173</v>
       </c>
       <c r="E39" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-09-02 19:06</v>
+        <v>2026-08-26 00:00</v>
       </c>
       <c r="G39" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H39" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I39" t="str">
         <v>10</v>
       </c>
       <c r="J39">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K39" t="str">
-        <v>CM -20260901-00000049</v>
+        <v>CM-20260826-00000055</v>
       </c>
       <c r="L39" t="str">
-        <v>N014-00001609</v>
+        <v>RFC-20260826-0006</v>
       </c>
       <c r="M39" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v/>
       </c>
       <c r="N39" t="str">
-        <v>RFC-20260902-003</v>
+        <v/>
       </c>
       <c r="O39" t="str">
-        <v/>
+        <v>Se utiliza 5 galones pendientes de N029-00001224 Y 5 g 0134003_AQ_Sarcasalones que se retiro N029-00001232, en Total 10 glns de faena</v>
       </c>
       <c r="P39" t="str">
-        <v>CHINCHA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q39" t="str">
         <v>PROPIO</v>
@@ -2605,52 +2605,52 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>139</v>
+        <v>32</v>
       </c>
       <c r="B40" t="str">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="C40" t="str">
-        <v>GL02COB</v>
+        <v>GL07COB</v>
       </c>
       <c r="D40" t="str">
-        <v>/api/evidencia/foto/7/comb-1788394745391/comb_0.jpg?v=1788394746</v>
+        <v>/api/evidencia/foto/7/comb-1787610099079/comb_0.jpg?v=1787610100</v>
       </c>
       <c r="E40" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>JOSE MIGUEL NINA ESQUIA</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-09-02 19:17</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G40" t="str">
         <v>GASTO</v>
       </c>
       <c r="H40" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I40" t="str">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K40" t="str">
-        <v>CM -20260901-00000049</v>
+        <v>CM-20260823-00000133</v>
       </c>
       <c r="L40" t="str">
-        <v>RFC-20260902-003</v>
+        <v>RFC-20260823-0021</v>
       </c>
       <c r="M40" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v/>
       </c>
       <c r="N40" t="str">
         <v/>
       </c>
       <c r="O40" t="str">
-        <v>SE CERRO LOS 10 GALONES</v>
+        <v>N034-00000377  0131298_TA_Boca_del_Rio se comsume 4gl</v>
       </c>
       <c r="P40" t="str">
-        <v>CHINCHA</v>
+        <v>TACNA</v>
       </c>
       <c r="Q40" t="str">
         <v>PROPIO</v>
@@ -2661,52 +2661,52 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="B41" t="str">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="C41" t="str">
-        <v>GL15HWI</v>
+        <v>GL02COB</v>
       </c>
       <c r="D41" t="str">
-        <v>/api/evidencia/foto/7/comb-1788455157389/comb_0.jpg?v=1788455162</v>
+        <v>/api/evidencia/foto/7/comb-1787611806002/comb_0.jpg?v=1787611407</v>
       </c>
       <c r="E41" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-09-03 12:03</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G41" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H41" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I41" t="str">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K41" t="str">
-        <v>CM-20260819-00000120</v>
+        <v>CM-20260822-00000057</v>
       </c>
       <c r="L41" t="str">
-        <v/>
+        <v>SITE 0133243 _IC_ BOGEGA_COW</v>
       </c>
       <c r="M41" t="str">
-        <v>0136549_AQ_Ccachaylla</v>
+        <v>SITE 0133243 _IC_ BOGEGA_COW</v>
       </c>
       <c r="N41" t="str">
-        <v>N031-00001169</v>
+        <v>N024-00002836</v>
       </c>
       <c r="O41" t="str">
-        <v>N031-00001169</v>
+        <v>SITE 0133243 _IC_ BOGEGA_COW</v>
       </c>
       <c r="P41" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q41" t="str">
         <v>PROPIO</v>
@@ -2717,52 +2717,52 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B42" t="str">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C42" t="str">
-        <v>GL15HWI</v>
+        <v>GL02COB</v>
       </c>
       <c r="D42" t="str">
-        <v>/api/evidencia/foto/7/comb-1788455245351/comb_0.jpg?v=1788455247</v>
+        <v>/api/evidencia/foto/7/comb-1788394180486/comb_0.jpg?v=1788394185</v>
       </c>
       <c r="E42" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-23 12:06</v>
+        <v>2026-09-02 19:06</v>
       </c>
       <c r="G42" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H42" t="str">
         <v>rllanos</v>
       </c>
       <c r="I42" t="str">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-250</v>
+        <v>40</v>
       </c>
       <c r="K42" t="str">
-        <v>CM-20260819-00000120</v>
+        <v>CM -20260901-00000049</v>
       </c>
       <c r="L42" t="str">
-        <v>N031-00001169</v>
+        <v>N014-00001609</v>
       </c>
       <c r="M42" t="str">
-        <v>0136549_AQ_Ccachaylla</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N42" t="str">
-        <v/>
+        <v>RFC-20260902-003</v>
       </c>
       <c r="O42" t="str">
-        <v>N031-00001169</v>
+        <v/>
       </c>
       <c r="P42" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q42" t="str">
         <v>PROPIO</v>
@@ -2773,52 +2773,52 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="B43" t="str">
-        <v>7</v>
+        <v>145</v>
       </c>
       <c r="C43" t="str">
-        <v>GL22COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D43" t="str">
-        <v>/api/evidencia/foto/7/7/comb_0.jpg?v=1787148418</v>
+        <v>/api/evidencia/foto/7/comb-1788394745391/comb_0.jpg?v=1788394746</v>
       </c>
       <c r="E43" t="str">
-        <v>ALEX DOMINGO ALVAREZ PUMA</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-18 00:00</v>
+        <v>2026-09-02 19:17</v>
       </c>
       <c r="G43" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H43" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I43" t="str">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K43" t="str">
-        <v>CM-20260818-00000117</v>
+        <v>CM -20260901-00000049</v>
       </c>
       <c r="L43" t="str">
-        <v/>
+        <v>RFC-20260902-003</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N43" t="str">
-        <v>N24-00000092</v>
+        <v/>
       </c>
       <c r="O43" t="str">
-        <v>CS_PRONAA_CUSCO pendiente foto factura</v>
+        <v>SE CERRO LOS 10 GALONES</v>
       </c>
       <c r="P43" t="str">
-        <v>CUZCO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q43" t="str">
         <v>PROPIO</v>
@@ -2829,108 +2829,108 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="B44" t="str">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="C44" t="str">
-        <v>GL18COB</v>
+        <v>GL15HWI</v>
       </c>
       <c r="D44" t="str">
-        <v>/api/evidencia/foto/7/comb-1787680547395/comb_0.jpg?v=1787680151</v>
+        <v>/api/evidencia/foto/7/comb-1788455157389/comb_0.jpg?v=1788455162</v>
       </c>
       <c r="E44" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-23 12:03</v>
       </c>
       <c r="G44" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H44" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I44" t="str">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="J44">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="K44" t="str">
-        <v>CM-20260823-00000396</v>
+        <v>CM-20260819-00000120</v>
       </c>
       <c r="L44" t="str">
-        <v>N024-00002843</v>
+        <v/>
       </c>
       <c r="M44" t="str">
-        <v>SITE 0134687_IC_Luis_Alvizuri</v>
+        <v>0136549_AQ_Ccachaylla</v>
       </c>
       <c r="N44" t="str">
-        <v>N024-00002843</v>
+        <v>N031-00001169</v>
       </c>
       <c r="O44" t="str">
-        <v>ATENCION CORTE PROGRAMADO SITE 0134687_IC_Luis_Alvizuri</v>
+        <v>N031-00001169</v>
       </c>
       <c r="P44" t="str">
-        <v>ICA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q44" t="str">
         <v>PROPIO</v>
       </c>
       <c r="R44" t="str">
-        <v/>
+        <v>hvargas</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="B45" t="str">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="C45" t="str">
-        <v>GL02COB</v>
+        <v>GL15HWI</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1788455245351/comb_0.jpg?v=1788455247</v>
       </c>
       <c r="E45" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-25 00:00</v>
+        <v>2026-08-23 12:06</v>
       </c>
       <c r="G45" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H45" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I45" t="str">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="J45">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K45" t="str">
-        <v>CM-20260822-00000057</v>
+        <v>CM-20260819-00000120</v>
       </c>
       <c r="L45" t="str">
-        <v>SE EMITE DESPUES DEL RETIRO</v>
+        <v>N031-00001169</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>0136549_AQ_Ccachaylla</v>
       </c>
       <c r="N45" t="str">
         <v/>
       </c>
       <c r="O45" t="str">
-        <v/>
+        <v>N031-00001169</v>
       </c>
       <c r="P45" t="str">
-        <v>CHINCHA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q45" t="str">
         <v>PROPIO</v>
@@ -2941,37 +2941,37 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B46" t="str">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="C46" t="str">
-        <v>GL04COB</v>
+        <v>GL22COB</v>
       </c>
       <c r="D46" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/7/comb_0.jpg?v=1787148418</v>
       </c>
       <c r="E46" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>ALEX DOMINGO ALVAREZ PUMA</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-18 00:00</v>
       </c>
       <c r="G46" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H46" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I46" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J46">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K46" t="str">
-        <v>CM-20260824-00000254</v>
+        <v>CM-20260818-00000117</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2980,13 +2980,13 @@
         <v/>
       </c>
       <c r="N46" t="str">
-        <v>SE EMITE DESOUES DE RETIRO</v>
+        <v>N24-00000092</v>
       </c>
       <c r="O46" t="str">
-        <v/>
+        <v>CS_PRONAA_CUSCO pendiente foto factura</v>
       </c>
       <c r="P46" t="str">
-        <v>AYACUCHO</v>
+        <v>CUZCO</v>
       </c>
       <c r="Q46" t="str">
         <v>PROPIO</v>
@@ -2997,55 +2997,55 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="B47" t="str">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="C47" t="str">
-        <v>GL01HWI</v>
+        <v>GL18COB</v>
       </c>
       <c r="D47" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787680547395/comb_0.jpg?v=1787680151</v>
       </c>
       <c r="E47" t="str">
         <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-09-03 10:25</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G47" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H47" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I47" t="str">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="J47">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="K47" t="str">
-        <v>CM-20260903-00000030</v>
+        <v>CM-20260823-00000396</v>
       </c>
       <c r="L47" t="str">
-        <v/>
+        <v>N024-00002843</v>
       </c>
       <c r="M47" t="str">
-        <v>0130840_IC_Rep_Marcona</v>
+        <v>SITE 0134687_IC_Luis_Alvizuri</v>
       </c>
       <c r="N47" t="str">
-        <v>SE EMITE DESPUES DE LA ATENCION</v>
+        <v>N024-00002843</v>
       </c>
       <c r="O47" t="str">
-        <v>ABASTECIMIENTO DE HIBRIDOS</v>
+        <v>ATENCION CORTE PROGRAMADO SITE 0134687_IC_Luis_Alvizuri</v>
       </c>
       <c r="P47" t="str">
         <v>ICA</v>
       </c>
       <c r="Q47" t="str">
-        <v>ENTEL</v>
+        <v>PROPIO</v>
       </c>
       <c r="R47" t="str">
         <v/>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B48" t="str">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="C48" t="str">
         <v>GL02COB</v>
@@ -3068,7 +3068,7 @@
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-18 00:00</v>
+        <v>2026-08-25 00:00</v>
       </c>
       <c r="G48" t="str">
         <v>INGRESO</v>
@@ -3083,10 +3083,10 @@
         <v>20</v>
       </c>
       <c r="K48" t="str">
-        <v>CM-20260817-00000221</v>
+        <v>CM-20260822-00000057</v>
       </c>
       <c r="L48" t="str">
-        <v/>
+        <v>SE EMITE DESPUES DEL RETIRO</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -3095,7 +3095,7 @@
         <v/>
       </c>
       <c r="O48" t="str">
-        <v>DESPUES SE ESTARA SUBIENDO LA NOTA DE VENTA</v>
+        <v/>
       </c>
       <c r="P48" t="str">
         <v>CHINCHA</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="B49" t="str">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="C49" t="str">
         <v>GL04COB</v>
@@ -3124,34 +3124,34 @@
         <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-09-04 11:46</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G49" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H49" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I49" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J49">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K49" t="str">
-        <v>CM-20260903-00000238</v>
+        <v>CM-20260824-00000254</v>
       </c>
       <c r="L49" t="str">
-        <v>se adjunta al cierre de la faena</v>
+        <v/>
       </c>
       <c r="M49" t="str">
-        <v>0134357_AY_Lecclespata</v>
+        <v/>
       </c>
       <c r="N49" t="str">
-        <v>se adjunta al cierre de la faena</v>
+        <v>SE EMITE DESOUES DE RETIRO</v>
       </c>
       <c r="O49" t="str">
-        <v>se adjunta al cierre de la faena</v>
+        <v/>
       </c>
       <c r="P49" t="str">
         <v>AYACUCHO</v>
@@ -3165,55 +3165,55 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B50" t="str">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C50" t="str">
-        <v>GL17COB</v>
+        <v>GL01HWI</v>
       </c>
       <c r="D50" t="str">
-        <v>/api/evidencia/foto/7/comb-1788540830072/comb_0.jpg?v=1788540832</v>
+        <v/>
       </c>
       <c r="E50" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-09-02 11:48</v>
+        <v>2026-09-03 10:25</v>
       </c>
       <c r="G50" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H50" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I50" t="str">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="K50" t="str">
-        <v>CM-20260902-00000023</v>
+        <v>CM-20260903-00000030</v>
       </c>
       <c r="L50" t="str">
-        <v>RFC-20260902-0006</v>
+        <v/>
       </c>
       <c r="M50" t="str">
-        <v>0130986_AQ_Pacuadros</v>
+        <v>0130840_IC_Rep_Marcona</v>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>SE EMITE DESPUES DE LA ATENCION</v>
       </c>
       <c r="O50" t="str">
-        <v>N029-00001311 Se consume 5gl</v>
+        <v>ABASTECIMIENTO DE HIBRIDOS</v>
       </c>
       <c r="P50" t="str">
-        <v>AREQUIPA</v>
+        <v>ICA</v>
       </c>
       <c r="Q50" t="str">
-        <v>PROPIO</v>
+        <v>ENTEL</v>
       </c>
       <c r="R50" t="str">
         <v/>
@@ -3221,22 +3221,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B51" t="str">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C51" t="str">
-        <v>GL02COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D51" t="str">
-        <v>/api/evidencia/foto/7/comb-1788540969483/comb_0.jpg?v=1788540972</v>
+        <v/>
       </c>
       <c r="E51" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-09-04 11:51</v>
+        <v>2026-09-04 11:46</v>
       </c>
       <c r="G51" t="str">
         <v>INGRESO</v>
@@ -3248,25 +3248,25 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K51" t="str">
-        <v>CM -20260903-00000217</v>
+        <v>CM-20260903-00000238</v>
       </c>
       <c r="L51" t="str">
-        <v>RFC-20260903</v>
+        <v>se adjunta al cierre de la faena</v>
       </c>
       <c r="M51" t="str">
-        <v>bodega</v>
+        <v>0134357_AY_Lecclespata</v>
       </c>
       <c r="N51" t="str">
-        <v/>
+        <v>se adjunta al cierre de la faena</v>
       </c>
       <c r="O51" t="str">
-        <v/>
+        <v>se adjunta al cierre de la faena</v>
       </c>
       <c r="P51" t="str">
-        <v>CHINCHA</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q51" t="str">
         <v>PROPIO</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B52" t="str">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C52" t="str">
         <v>GL17COB</v>
       </c>
       <c r="D52" t="str">
-        <v>/api/evidencia/foto/7/comb-1788541138254/comb_0.jpg?v=1788541140</v>
+        <v>/api/evidencia/foto/7/comb-1788540830072/comb_0.jpg?v=1788540832</v>
       </c>
       <c r="E52" t="str">
-        <v>VICTOR IGNACIO ORTEGA ALAVE</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F52" t="str">
-        <v>2026-09-02 11:56</v>
+        <v>2026-09-02 11:48</v>
       </c>
       <c r="G52" t="str">
         <v>GASTO</v>
@@ -3301,25 +3301,25 @@
         <v>ygalvez</v>
       </c>
       <c r="I52" t="str">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="K52" t="str">
-        <v>CM-20260902-00000085</v>
+        <v>CM-20260902-00000023</v>
       </c>
       <c r="L52" t="str">
-        <v>RFC-20260902-0005</v>
+        <v>RFC-20260902-0006</v>
       </c>
       <c r="M52" t="str">
-        <v>0133920_AQ_Zona_Enriquez</v>
+        <v>0130986_AQ_Pacuadros</v>
       </c>
       <c r="N52" t="str">
         <v/>
       </c>
       <c r="O52" t="str">
-        <v>N020-00003415 Se consume 8gl de factura de VÍctor Ortega</v>
+        <v>N029-00001311 Se consume 5gl</v>
       </c>
       <c r="P52" t="str">
         <v>AREQUIPA</v>
@@ -3333,25 +3333,25 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B53" t="str">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C53" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D53" t="str">
-        <v>/api/evidencia/foto/7/comb-1788541285905/comb_0.jpg?v=1788541289</v>
+        <v>/api/evidencia/foto/7/comb-1788540969483/comb_0.jpg?v=1788540972</v>
       </c>
       <c r="E53" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F53" t="str">
-        <v>2026-09-04 11:56</v>
+        <v>2026-09-04 11:51</v>
       </c>
       <c r="G53" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H53" t="str">
         <v>rllanos</v>
@@ -3360,22 +3360,22 @@
         <v>10</v>
       </c>
       <c r="J53">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="K53" t="str">
         <v>CM -20260903-00000217</v>
       </c>
       <c r="L53" t="str">
-        <v>RFC-20260034</v>
+        <v>RFC-20260903</v>
       </c>
       <c r="M53" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v>bodega</v>
       </c>
       <c r="N53" t="str">
         <v/>
       </c>
       <c r="O53" t="str">
-        <v>ya tenia 2 galones se les agrego 8 suma 10 galones</v>
+        <v/>
       </c>
       <c r="P53" t="str">
         <v>CHINCHA</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B54" t="str">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C54" t="str">
-        <v>GL23COB</v>
+        <v>GL17COB</v>
       </c>
       <c r="D54" t="str">
-        <v>/api/evidencia/foto/7/comb-1788542288971/comb_0.jpg?v=1788542289</v>
+        <v>/api/evidencia/foto/7/comb-1788541138254/comb_0.jpg?v=1788541140</v>
       </c>
       <c r="E54" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>VICTOR IGNACIO ORTEGA ALAVE</v>
       </c>
       <c r="F54" t="str">
-        <v>2026-09-02 17:16</v>
+        <v>2026-09-02 11:56</v>
       </c>
       <c r="G54" t="str">
         <v>GASTO</v>
@@ -3413,25 +3413,25 @@
         <v>ygalvez</v>
       </c>
       <c r="I54" t="str">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J54">
-        <v>5.2</v>
+        <v>-5</v>
       </c>
       <c r="K54" t="str">
-        <v>CM-20260902-00000073</v>
+        <v>CM-20260902-00000085</v>
       </c>
       <c r="L54" t="str">
-        <v>RFC-20260902-0018</v>
+        <v>RFC-20260902-0005</v>
       </c>
       <c r="M54" t="str">
-        <v>0133932_AQ_Puerto_Rico_Aqp</v>
+        <v>0133920_AQ_Zona_Enriquez</v>
       </c>
       <c r="N54" t="str">
         <v/>
       </c>
       <c r="O54" t="str">
-        <v>N020-00003521 Se usa 3gl</v>
+        <v>N020-00003415 Se consume 8gl de factura de VÍctor Ortega</v>
       </c>
       <c r="P54" t="str">
         <v>AREQUIPA</v>
@@ -3445,52 +3445,52 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B55" t="str">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C55" t="str">
-        <v>GL23COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D55" t="str">
-        <v>/api/evidencia/foto/7/comb-1788542800380/comb_0.jpg?v=1788542800</v>
+        <v>/api/evidencia/foto/7/comb-1788541285905/comb_0.jpg?v=1788541289</v>
       </c>
       <c r="E55" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F55" t="str">
-        <v>2026-09-02 18:22</v>
+        <v>2026-09-04 11:56</v>
       </c>
       <c r="G55" t="str">
         <v>GASTO</v>
       </c>
       <c r="H55" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I55" t="str">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J55">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="K55" t="str">
-        <v>CM-20260902-00000097</v>
+        <v>CM -20260903-00000217</v>
       </c>
       <c r="L55" t="str">
-        <v>RFC-20260902-0033</v>
+        <v>RFC-20260034</v>
       </c>
       <c r="M55" t="str">
-        <v>013141776_AQ_MiradorCayma</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N55" t="str">
         <v/>
       </c>
       <c r="O55" t="str">
-        <v>N029-00001304 Se consume 3gl</v>
+        <v>ya tenia 2 galones se les agrego 8 suma 10 galones</v>
       </c>
       <c r="P55" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q55" t="str">
         <v>PROPIO</v>
@@ -3501,52 +3501,52 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B56" t="str">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C56" t="str">
-        <v>GL04COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D56" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1788542288971/comb_0.jpg?v=1788542289</v>
       </c>
       <c r="E56" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F56" t="str">
-        <v>2026-09-04 12:48</v>
+        <v>2026-09-02 17:16</v>
       </c>
       <c r="G56" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H56" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I56" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J56">
-        <v>16</v>
+        <v>5.2</v>
       </c>
       <c r="K56" t="str">
-        <v>CM-20260903-000001218</v>
+        <v>CM-20260902-00000073</v>
       </c>
       <c r="L56" t="str">
-        <v>SE EMITE AL TERMINODE FAENA</v>
+        <v>RFC-20260902-0018</v>
       </c>
       <c r="M56" t="str">
-        <v>0134357_AY_Lecclespata</v>
+        <v>0133932_AQ_Puerto_Rico_Aqp</v>
       </c>
       <c r="N56" t="str">
         <v/>
       </c>
       <c r="O56" t="str">
-        <v>SE EMITE AL TERMINODE FAENA</v>
+        <v>N020-00003521 Se usa 3gl</v>
       </c>
       <c r="P56" t="str">
-        <v>AYACUCHO</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q56" t="str">
         <v>PROPIO</v>
@@ -3557,52 +3557,52 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B57" t="str">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C57" t="str">
-        <v>GL04COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D57" t="str">
-        <v>/api/evidencia/foto/7/comb-1788544404187/comb_0.jpg?v=1788544407</v>
+        <v>/api/evidencia/foto/7/comb-1788542800380/comb_0.jpg?v=1788542800</v>
       </c>
       <c r="E57" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F57" t="str">
-        <v>2026-09-03 12:49</v>
+        <v>2026-09-02 18:22</v>
       </c>
       <c r="G57" t="str">
         <v>GASTO</v>
       </c>
       <c r="H57" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I57" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J57">
-        <v>-2</v>
+        <v>2.2</v>
       </c>
       <c r="K57" t="str">
-        <v>CM-20260903-0000218</v>
+        <v>CM-20260902-00000097</v>
       </c>
       <c r="L57" t="str">
-        <v>N007-00000388</v>
+        <v>RFC-20260902-0033</v>
       </c>
       <c r="M57" t="str">
-        <v>0134357_AY_Lecclespata</v>
+        <v>013141776_AQ_MiradorCayma</v>
       </c>
       <c r="N57" t="str">
         <v/>
       </c>
       <c r="O57" t="str">
-        <v>SE SOLICITO 8 Y SOLO SE RETIRO 6</v>
+        <v>N029-00001304 Se consume 3gl</v>
       </c>
       <c r="P57" t="str">
-        <v>AYACUCHO</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q57" t="str">
         <v>PROPIO</v>
@@ -3613,22 +3613,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B58" t="str">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C58" t="str">
-        <v>GL02COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D58" t="str">
-        <v>/api/evidencia/foto/7/comb-1788545582403/comb_0.jpg?v=1788545585</v>
+        <v/>
       </c>
       <c r="E58" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F58" t="str">
-        <v>2026-09-04 13:04</v>
+        <v>2026-09-04 12:48</v>
       </c>
       <c r="G58" t="str">
         <v>INGRESO</v>
@@ -3637,28 +3637,28 @@
         <v>rllanos</v>
       </c>
       <c r="I58" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K58" t="str">
-        <v>CM-20260902-00000270</v>
+        <v>CM-20260903-000001218</v>
       </c>
       <c r="L58" t="str">
-        <v>RFC-20260902-0029</v>
+        <v>SE EMITE AL TERMINODE FAENA</v>
       </c>
       <c r="M58" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v>0134357_AY_Lecclespata</v>
       </c>
       <c r="N58" t="str">
-        <v>N014-00001617</v>
+        <v/>
       </c>
       <c r="O58" t="str">
-        <v/>
+        <v>SE EMITE AL TERMINODE FAENA</v>
       </c>
       <c r="P58" t="str">
-        <v>CHINCHA</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q58" t="str">
         <v>PROPIO</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B59" t="str">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C59" t="str">
-        <v>GL02COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D59" t="str">
-        <v>/api/evidencia/foto/7/comb-1788545662689/comb_0.jpg?v=1788545664</v>
+        <v>/api/evidencia/foto/7/comb-1788544404187/comb_0.jpg?v=1788544407</v>
       </c>
       <c r="E59" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F59" t="str">
-        <v>2026-09-03 13:13</v>
+        <v>2026-09-03 12:49</v>
       </c>
       <c r="G59" t="str">
         <v>GASTO</v>
@@ -3693,28 +3693,28 @@
         <v>rllanos</v>
       </c>
       <c r="I59" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="K59" t="str">
-        <v>CM -20260902-00000270</v>
+        <v>CM-20260903-0000218</v>
       </c>
       <c r="L59" t="str">
-        <v>N014-00001617</v>
+        <v>N007-00000388</v>
       </c>
       <c r="M59" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v>0134357_AY_Lecclespata</v>
       </c>
       <c r="N59" t="str">
         <v/>
       </c>
       <c r="O59" t="str">
-        <v>SE REALIZA RENDICION DE 10 GLNS  PARA ATENCION DE  CM -20260902-00000270  PARA EL SITE IC_BODEGA_COW</v>
+        <v>SE SOLICITO 8 Y SOLO SE RETIRO 6</v>
       </c>
       <c r="P59" t="str">
-        <v>CHINCHA</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q59" t="str">
         <v>PROPIO</v>
@@ -3725,52 +3725,52 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="B60" t="str">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="C60" t="str">
-        <v>GL24COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D60" t="str">
-        <v>/api/evidencia/foto/7/comb-1787335877546/comb_0.jpg?v=1787335879</v>
+        <v>/api/evidencia/foto/7/comb-1788545582403/comb_0.jpg?v=1788545585</v>
       </c>
       <c r="E60" t="str">
-        <v>YOVANIE ENRIQUEZ CASTILLO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F60" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-09-04 13:04</v>
       </c>
       <c r="G60" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H60" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I60" t="str">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K60" t="str">
-        <v>CM-20260820-00000121</v>
+        <v>CM-20260902-00000270</v>
       </c>
       <c r="L60" t="str">
-        <v/>
+        <v>RFC-20260902-0029</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N60" t="str">
-        <v/>
+        <v>N014-00001617</v>
       </c>
       <c r="O60" t="str">
-        <v>RFC-20260820-0011 0132754_CS_Kucya N574-00037928 Se consume 9.25</v>
+        <v/>
       </c>
       <c r="P60" t="str">
-        <v>CUZCO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q60" t="str">
         <v>PROPIO</v>
@@ -3781,49 +3781,49 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="B61" t="str">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="C61" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D61" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1788545662689/comb_0.jpg?v=1788545664</v>
       </c>
       <c r="E61" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F61" t="str">
-        <v>2026-08-31 11:37</v>
+        <v>2026-09-03 13:13</v>
       </c>
       <c r="G61" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H61" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I61" t="str">
         <v>10</v>
       </c>
       <c r="J61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>CM -20260902-00000270</v>
       </c>
       <c r="L61" t="str">
-        <v/>
+        <v>N014-00001617</v>
       </c>
       <c r="M61" t="str">
         <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N61" t="str">
-        <v>SE EMITE DESPUES DEL RETIRO</v>
+        <v/>
       </c>
       <c r="O61" t="str">
-        <v/>
+        <v>SE REALIZA RENDICION DE 10 GLNS  PARA ATENCION DE  CM -20260902-00000270  PARA EL SITE IC_BODEGA_COW</v>
       </c>
       <c r="P61" t="str">
         <v>CHINCHA</v>
@@ -3837,52 +3837,52 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="B62" t="str">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="C62" t="str">
-        <v>GL02COB</v>
+        <v>GL24COB</v>
       </c>
       <c r="D62" t="str">
-        <v>/api/evidencia/foto/7/comb-1788281026722/comb_0.jpg?v=1788280619</v>
+        <v>/api/evidencia/foto/7/comb-1787335877546/comb_0.jpg?v=1787335879</v>
       </c>
       <c r="E62" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>YOVANIE ENRIQUEZ CASTILLO</v>
       </c>
       <c r="F62" t="str">
-        <v>2026-08-31 11:42</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G62" t="str">
         <v>GASTO</v>
       </c>
       <c r="H62" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I62" t="str">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>9.95</v>
       </c>
       <c r="K62" t="str">
-        <v>CM-20260829-00000043</v>
+        <v>CM-20260820-00000121</v>
       </c>
       <c r="L62" t="str">
-        <v>N014-00001587</v>
+        <v/>
       </c>
       <c r="M62" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v/>
       </c>
       <c r="N62" t="str">
-        <v>N014-00001587</v>
+        <v/>
       </c>
       <c r="O62" t="str">
-        <v>SE ABSTECIO 10  GLS</v>
+        <v>RFC-20260820-0011 0132754_CS_Kucya N574-00037928 Se consume 9.25</v>
       </c>
       <c r="P62" t="str">
-        <v>CHINCHA</v>
+        <v>CUZCO</v>
       </c>
       <c r="Q62" t="str">
         <v>PROPIO</v>
@@ -3893,25 +3893,25 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B63" t="str">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C63" t="str">
-        <v>GL18COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D63" t="str">
-        <v>/api/evidencia/foto/7/comb-1788281585946/comb_0.jpg?v=1788281178</v>
+        <v/>
       </c>
       <c r="E63" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F63" t="str">
-        <v>2026-08-31 11:47</v>
+        <v>2026-08-31 11:37</v>
       </c>
       <c r="G63" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H63" t="str">
         <v>lgutierrez</v>
@@ -3920,25 +3920,25 @@
         <v>10</v>
       </c>
       <c r="J63">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K63" t="str">
-        <v>CM-20260830-00000265</v>
+        <v/>
       </c>
       <c r="L63" t="str">
-        <v>N10-00000531</v>
+        <v/>
       </c>
       <c r="M63" t="str">
-        <v>0134672_IC_Avenida_Siete</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N63" t="str">
-        <v>N10-00000531</v>
+        <v>SE EMITE DESPUES DEL RETIRO</v>
       </c>
       <c r="O63" t="str">
-        <v>SE REALIZO ABASTECIMIENTO DE 10 GLS</v>
+        <v/>
       </c>
       <c r="P63" t="str">
-        <v>ICA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q63" t="str">
         <v>PROPIO</v>
@@ -3949,52 +3949,52 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="B64" t="str">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="C64" t="str">
-        <v>GL23COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D64" t="str">
-        <v>/api/evidencia/foto/7/comb-1787602020917/comb_0.jpg?v=1787602022</v>
+        <v>/api/evidencia/foto/7/comb-1788281026722/comb_0.jpg?v=1788280619</v>
       </c>
       <c r="E64" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F64" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-31 11:42</v>
       </c>
       <c r="G64" t="str">
         <v>GASTO</v>
       </c>
       <c r="H64" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I64" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K64" t="str">
-        <v>CM-20260819-00000056</v>
+        <v>CM-20260829-00000043</v>
       </c>
       <c r="L64" t="str">
-        <v>RFC-20260821-0003</v>
+        <v>N014-00001587</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N64" t="str">
-        <v/>
+        <v>N014-00001587</v>
       </c>
       <c r="O64" t="str">
-        <v>0134389_AQ_El_Carmen_AQP N029-00001191</v>
+        <v>SE ABSTECIO 10  GLS</v>
       </c>
       <c r="P64" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q64" t="str">
         <v>PROPIO</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="B65" t="str">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="C65" t="str">
-        <v>GL04COB</v>
+        <v>GL18COB</v>
       </c>
       <c r="D65" t="str">
-        <v>/api/evidencia/foto/7/comb-1787602876704/comb_0.jpg?v=1787602478</v>
+        <v>/api/evidencia/foto/7/comb-1788281585946/comb_0.jpg?v=1788281178</v>
       </c>
       <c r="E65" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F65" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-31 11:47</v>
       </c>
       <c r="G65" t="str">
         <v>GASTO</v>
@@ -4029,28 +4029,28 @@
         <v>lgutierrez</v>
       </c>
       <c r="I65" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K65" t="str">
-        <v>CM-20260823-00000076</v>
+        <v>CM-20260830-00000265</v>
       </c>
       <c r="L65" t="str">
-        <v>site 0133729 _ay_Aeropuerto_Mendivil</v>
+        <v>N10-00000531</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>0134672_IC_Avenida_Siete</v>
       </c>
       <c r="N65" t="str">
-        <v>N0007-00000365</v>
+        <v>N10-00000531</v>
       </c>
       <c r="O65" t="str">
-        <v>SE LIQUIDO 8 GLS (REALIZADO X EMANUEL)</v>
+        <v>SE REALIZO ABASTECIMIENTO DE 10 GLS</v>
       </c>
       <c r="P65" t="str">
-        <v>AYACUCHO</v>
+        <v>ICA</v>
       </c>
       <c r="Q65" t="str">
         <v>PROPIO</v>
@@ -4061,52 +4061,52 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="B66" t="str">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="C66" t="str">
-        <v>GL18COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D66" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787602020917/comb_0.jpg?v=1787602022</v>
       </c>
       <c r="E66" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F66" t="str">
-        <v>2026-09-02 09:46</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G66" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H66" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I66" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J66">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K66" t="str">
-        <v>CM 20360901-00000251</v>
+        <v>CM-20260819-00000056</v>
       </c>
       <c r="L66" t="str">
-        <v/>
+        <v>RFC-20260821-0003</v>
       </c>
       <c r="M66" t="str">
-        <v>0134672_IC_Avenida_Siete</v>
+        <v/>
       </c>
       <c r="N66" t="str">
-        <v>se emite despues de l retiro</v>
+        <v/>
       </c>
       <c r="O66" t="str">
-        <v/>
+        <v>0134389_AQ_El_Carmen_AQP N029-00001191</v>
       </c>
       <c r="P66" t="str">
-        <v>ICA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q66" t="str">
         <v>PROPIO</v>
@@ -4117,52 +4117,52 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>128</v>
+        <v>40</v>
       </c>
       <c r="B67" t="str">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="C67" t="str">
-        <v>GL02COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D67" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787602876704/comb_0.jpg?v=1787602478</v>
       </c>
       <c r="E67" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F67" t="str">
-        <v>2026-09-01 09:47</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G67" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H67" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I67" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J67">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K67" t="str">
-        <v>CM-20260901-00000049</v>
+        <v>CM-20260823-00000076</v>
       </c>
       <c r="L67" t="str">
-        <v/>
+        <v>site 0133729 _ay_Aeropuerto_Mendivil</v>
       </c>
       <c r="M67" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v/>
       </c>
       <c r="N67" t="str">
-        <v>se emite despues del retiro</v>
+        <v>N0007-00000365</v>
       </c>
       <c r="O67" t="str">
-        <v/>
+        <v>SE LIQUIDO 8 GLS (REALIZADO X EMANUEL)</v>
       </c>
       <c r="P67" t="str">
-        <v>CHINCHA</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q67" t="str">
         <v>PROPIO</v>
@@ -4173,52 +4173,52 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B68" t="str">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C68" t="str">
-        <v>GL04COB</v>
+        <v>GL18COB</v>
       </c>
       <c r="D68" t="str">
-        <v>/api/evidencia/foto/7/comb-1788283092833/comb_0.jpg?v=1788282685</v>
+        <v/>
       </c>
       <c r="E68" t="str">
-        <v>EMANUEL SAMUEL CONTRERAS ZEGARRA</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F68" t="str">
-        <v>2026-08-31 12:17</v>
+        <v>2026-09-02 09:46</v>
       </c>
       <c r="G68" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H68" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I68" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K68" t="str">
-        <v>CM-20260831-00000209</v>
+        <v>CM 20360901-00000251</v>
       </c>
       <c r="L68" t="str">
-        <v>N007-00000368</v>
+        <v/>
       </c>
       <c r="M68" t="str">
-        <v>0133729_AY_Aeropuerto_Mendivil</v>
+        <v>0134672_IC_Avenida_Siete</v>
       </c>
       <c r="N68" t="str">
-        <v>N007-00000368</v>
+        <v>se emite despues de l retiro</v>
       </c>
       <c r="O68" t="str">
-        <v>SE ABASTECIO 4 GLS DEL RETIRO DE LOS 8 GLS DEL DIA 24.08 CON CM 2026-00000254</v>
+        <v/>
       </c>
       <c r="P68" t="str">
-        <v>AYACUCHO</v>
+        <v>ICA</v>
       </c>
       <c r="Q68" t="str">
         <v>PROPIO</v>
@@ -4229,22 +4229,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="B69" t="str">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="C69" t="str">
-        <v>GL18COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D69" t="str">
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F69" t="str">
-        <v>2026-08-22 00:00</v>
+        <v>2026-09-01 09:47</v>
       </c>
       <c r="G69" t="str">
         <v>INGRESO</v>
@@ -4253,28 +4253,28 @@
         <v>lgutierrez</v>
       </c>
       <c r="I69" t="str">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J69">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>CM-20260901-00000049</v>
       </c>
       <c r="L69" t="str">
         <v/>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N69" t="str">
-        <v>X EMITIR AL RETIRAR</v>
+        <v>se emite despues del retiro</v>
       </c>
       <c r="O69" t="str">
-        <v>Site: IC_LUIS ALVISURI</v>
+        <v/>
       </c>
       <c r="P69" t="str">
-        <v>ICA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q69" t="str">
         <v>PROPIO</v>
@@ -4285,52 +4285,52 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B70" t="str">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C70" t="str">
-        <v>GL23COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D70" t="str">
-        <v>/api/evidencia/foto/7/comb-1788377037561/comb_0.jpg?v=1788377038</v>
+        <v>/api/evidencia/foto/7/comb-1788283092833/comb_0.jpg?v=1788282685</v>
       </c>
       <c r="E70" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>EMANUEL SAMUEL CONTRERAS ZEGARRA</v>
       </c>
       <c r="F70" t="str">
-        <v>2026-09-02 14:19</v>
+        <v>2026-08-31 12:17</v>
       </c>
       <c r="G70" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H70" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I70" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70">
-        <v>8.2</v>
+        <v>4</v>
       </c>
       <c r="K70" t="str">
-        <v>CM-20260902-00000097</v>
+        <v>CM-20260831-00000209</v>
       </c>
       <c r="L70" t="str">
-        <v/>
+        <v>N007-00000368</v>
       </c>
       <c r="M70" t="str">
-        <v>013933_ puerto rico_AQP</v>
+        <v>0133729_AY_Aeropuerto_Mendivil</v>
       </c>
       <c r="N70" t="str">
-        <v>N029-00001304</v>
+        <v>N007-00000368</v>
       </c>
       <c r="O70" t="str">
-        <v>N029-00001304 SE RETIRA 5GL</v>
+        <v>SE ABASTECIO 4 GLS DEL RETIRO DE LOS 8 GLS DEL DIA 24.08 CON CM 2026-00000254</v>
       </c>
       <c r="P70" t="str">
-        <v>AREQUIPA</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q70" t="str">
         <v>PROPIO</v>
@@ -4341,49 +4341,49 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B71" t="str">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C71" t="str">
         <v>GL18COB</v>
       </c>
       <c r="D71" t="str">
-        <v>/api/evidencia/foto/7/comb-1787672695962/comb_0.jpg?v=1787672296</v>
+        <v/>
       </c>
       <c r="E71" t="str">
         <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F71" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-22 00:00</v>
       </c>
       <c r="G71" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H71" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I71" t="str">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="J71">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K71" t="str">
-        <v>CM-20260823-00000122</v>
+        <v/>
       </c>
       <c r="L71" t="str">
-        <v>SITE 0134393_IC_Fermin_Tanguis</v>
+        <v/>
       </c>
       <c r="M71" t="str">
-        <v>0134393_IC_Fermin_Tanguis</v>
+        <v/>
       </c>
       <c r="N71" t="str">
-        <v>N024-00002843</v>
+        <v>X EMITIR AL RETIRAR</v>
       </c>
       <c r="O71" t="str">
-        <v>ATENCION CORTE PROGRAMADO SITE 0134393_IC_Fermin_Tanguis</v>
+        <v>Site: IC_LUIS ALVISURI</v>
       </c>
       <c r="P71" t="str">
         <v>ICA</v>
@@ -4397,22 +4397,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="B72" t="str">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="C72" t="str">
-        <v>GL17COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D72" t="str">
-        <v>/api/evidencia/foto/7/comb-1787766631685/comb_0.jpg?v=1787766633</v>
+        <v>/api/evidencia/foto/7/comb-1788377037561/comb_0.jpg?v=1788377038</v>
       </c>
       <c r="E72" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F72" t="str">
-        <v>2026-08-26 00:00</v>
+        <v>2026-09-02 14:19</v>
       </c>
       <c r="G72" t="str">
         <v>INGRESO</v>
@@ -4424,22 +4424,22 @@
         <v>5</v>
       </c>
       <c r="J72">
-        <v>18</v>
+        <v>8.2</v>
       </c>
       <c r="K72" t="str">
-        <v>CM-20260826-00000055</v>
+        <v>CM-20260902-00000097</v>
       </c>
       <c r="L72" t="str">
-        <v>RFC-20260826-0006</v>
+        <v/>
       </c>
       <c r="M72" t="str">
-        <v/>
+        <v>013933_ puerto rico_AQP</v>
       </c>
       <c r="N72" t="str">
-        <v>N029-00001232</v>
+        <v>N029-00001304</v>
       </c>
       <c r="O72" t="str">
-        <v>0134003_AQ_Sarcas  N029-00001232 se retira 5 gl</v>
+        <v>N029-00001304 SE RETIRA 5GL</v>
       </c>
       <c r="P72" t="str">
         <v>AREQUIPA</v>
@@ -4453,52 +4453,52 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B73" t="str">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C73" t="str">
-        <v>GL23COB</v>
+        <v>GL18COB</v>
       </c>
       <c r="D73" t="str">
-        <v>/api/evidencia/foto/7/64/comb_0.jpg?v=1787694218</v>
+        <v>/api/evidencia/foto/7/comb-1787672695962/comb_0.jpg?v=1787672296</v>
       </c>
       <c r="E73" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F73" t="str">
-        <v>2026-08-25 00:00</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G73" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H73" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I73" t="str">
         <v>5</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K73" t="str">
-        <v>CM-20260825-00000111</v>
+        <v>CM-20260823-00000122</v>
       </c>
       <c r="L73" t="str">
-        <v/>
+        <v>SITE 0134393_IC_Fermin_Tanguis</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>0134393_IC_Fermin_Tanguis</v>
       </c>
       <c r="N73" t="str">
-        <v>N025-00006024</v>
+        <v>N024-00002843</v>
       </c>
       <c r="O73" t="str">
-        <v>013140333_AQ_Horeb N025-00006024 5GL</v>
+        <v>ATENCION CORTE PROGRAMADO SITE 0134393_IC_Fermin_Tanguis</v>
       </c>
       <c r="P73" t="str">
-        <v>AREQUIPA</v>
+        <v>ICA</v>
       </c>
       <c r="Q73" t="str">
         <v>PROPIO</v>
@@ -4509,22 +4509,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="B74" t="str">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="C74" t="str">
         <v>GL17COB</v>
       </c>
       <c r="D74" t="str">
-        <v>/api/evidencia/foto/7/comb-1788377627409/comb_0.jpg?v=1788377627</v>
+        <v>/api/evidencia/foto/7/comb-1787766631685/comb_0.jpg?v=1787766633</v>
       </c>
       <c r="E74" t="str">
         <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F74" t="str">
-        <v>2026-09-02 14:31</v>
+        <v>2026-08-26 00:00</v>
       </c>
       <c r="G74" t="str">
         <v>INGRESO</v>
@@ -4533,25 +4533,25 @@
         <v>ygalvez</v>
       </c>
       <c r="I74" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K74" t="str">
-        <v>CM-20260902-00000023</v>
+        <v>CM-20260826-00000055</v>
       </c>
       <c r="L74" t="str">
-        <v/>
+        <v>RFC-20260826-0006</v>
       </c>
       <c r="M74" t="str">
-        <v>0130986_AQ_Pacuadros</v>
+        <v/>
       </c>
       <c r="N74" t="str">
-        <v>N029-00001311</v>
+        <v>N029-00001232</v>
       </c>
       <c r="O74" t="str">
-        <v>N029-00001311 SE RETIRAN 1O GL</v>
+        <v>0134003_AQ_Sarcas  N029-00001232 se retira 5 gl</v>
       </c>
       <c r="P74" t="str">
         <v>AREQUIPA</v>
@@ -4565,52 +4565,52 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="B75" t="str">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="C75" t="str">
-        <v>GL02COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D75" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/64/comb_0.jpg?v=1787694218</v>
       </c>
       <c r="E75" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F75" t="str">
-        <v>2026-08-28 14:43</v>
+        <v>2026-08-25 00:00</v>
       </c>
       <c r="G75" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H75" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I75" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K75" t="str">
-        <v>CM-20260828-00000240</v>
+        <v>CM-20260825-00000111</v>
       </c>
       <c r="L75" t="str">
-        <v>SE EMOITE DESPUES DEL RETIRO</v>
+        <v/>
       </c>
       <c r="M75" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v/>
       </c>
       <c r="N75" t="str">
-        <v/>
+        <v>N025-00006024</v>
       </c>
       <c r="O75" t="str">
-        <v/>
+        <v>013140333_AQ_Horeb N025-00006024 5GL</v>
       </c>
       <c r="P75" t="str">
-        <v>CHINCHA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q75" t="str">
         <v>PROPIO</v>
@@ -4621,52 +4621,52 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="B76" t="str">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="C76" t="str">
-        <v>GL09COB</v>
+        <v>GL17COB</v>
       </c>
       <c r="D76" t="str">
-        <v>/api/evidencia/foto/7/comb-1787603535205/comb_0.jpg?v=1787603135</v>
+        <v>/api/evidencia/foto/7/comb-1788377627409/comb_0.jpg?v=1788377627</v>
       </c>
       <c r="E76" t="str">
-        <v>BRIAN JESUS CABRERA ASCENCIO</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F76" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-09-02 14:31</v>
       </c>
       <c r="G76" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H76" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I76" t="str">
         <v>10</v>
       </c>
       <c r="J76">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K76" t="str">
-        <v>CM-20260823-00000107</v>
+        <v>CM-20260902-00000023</v>
       </c>
       <c r="L76" t="str">
-        <v>RETIRADA 30 GLS PERO EN ESTA ATENCION ESTA 10 GLS</v>
+        <v/>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>0130986_AQ_Pacuadros</v>
       </c>
       <c r="N76" t="str">
-        <v>N016-00002175</v>
+        <v>N029-00001311</v>
       </c>
       <c r="O76" t="str">
-        <v>CORTE PROGRAMADO 0133207_IC_Victoria_Pisco</v>
+        <v>N029-00001311 SE RETIRAN 1O GL</v>
       </c>
       <c r="P76" t="str">
-        <v>ICA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q76" t="str">
         <v>PROPIO</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="B77" t="str">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="C77" t="str">
         <v>GL02COB</v>
@@ -4692,7 +4692,7 @@
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F77" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-08-28 14:43</v>
       </c>
       <c r="G77" t="str">
         <v>INGRESO</v>
@@ -4704,22 +4704,22 @@
         <v>10</v>
       </c>
       <c r="J77">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K77" t="str">
-        <v>CM-20260820-00000060</v>
+        <v>CM-20260828-00000240</v>
       </c>
       <c r="L77" t="str">
-        <v/>
+        <v>SE EMOITE DESPUES DEL RETIRO</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N77" t="str">
         <v/>
       </c>
       <c r="O77" t="str">
-        <v>SITE BODEGA COW</v>
+        <v/>
       </c>
       <c r="P77" t="str">
         <v>CHINCHA</v>
@@ -4733,52 +4733,52 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="B78" t="str">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="C78" t="str">
-        <v>GL02COB</v>
+        <v>GL09COB</v>
       </c>
       <c r="D78" t="str">
-        <v>/api/evidencia/foto/7/comb-1788378643048/comb_0.jpg?v=1788378645</v>
+        <v>/api/evidencia/foto/7/comb-1787603535205/comb_0.jpg?v=1787603135</v>
       </c>
       <c r="E78" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>BRIAN JESUS CABRERA ASCENCIO</v>
       </c>
       <c r="F78" t="str">
-        <v>2026-09-02 14:50</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G78" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H78" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I78" t="str">
         <v>10</v>
       </c>
       <c r="J78">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K78" t="str">
-        <v>CM-20260829-00000043</v>
+        <v>CM-20260823-00000107</v>
       </c>
       <c r="L78" t="str">
-        <v>N014-00001570</v>
+        <v>RETIRADA 30 GLS PERO EN ESTA ATENCION ESTA 10 GLS</v>
       </c>
       <c r="M78" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v/>
       </c>
       <c r="N78" t="str">
-        <v>N014-00001570</v>
+        <v>N016-00002175</v>
       </c>
       <c r="O78" t="str">
-        <v>SE CONSUMIO LOS 10 GALONES</v>
+        <v>CORTE PROGRAMADO 0133207_IC_Victoria_Pisco</v>
       </c>
       <c r="P78" t="str">
-        <v>CHINCHA</v>
+        <v>ICA</v>
       </c>
       <c r="Q78" t="str">
         <v>PROPIO</v>
@@ -4789,25 +4789,25 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B79" t="str">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C79" t="str">
-        <v>GL09COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D79" t="str">
-        <v>/api/evidencia/foto/7/comb-1787668039002/comb_0.jpg?v=1787667639</v>
+        <v/>
       </c>
       <c r="E79" t="str">
-        <v>BRIAN JESUS CABRERA ASCENCIO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F79" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G79" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H79" t="str">
         <v>lgutierrez</v>
@@ -4816,25 +4816,25 @@
         <v>10</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K79" t="str">
-        <v>CM-20260824-00000197</v>
+        <v>CM-20260820-00000060</v>
       </c>
       <c r="L79" t="str">
-        <v>N024-00002842</v>
+        <v/>
       </c>
       <c r="M79" t="str">
-        <v>0132239_IC_Baldelomar_1900</v>
+        <v/>
       </c>
       <c r="N79" t="str">
-        <v>N024-00002842</v>
+        <v/>
       </c>
       <c r="O79" t="str">
-        <v>ATENCION CORTE PROGRAMADO AFENA ECHO POR YAIR ESCAJADILLO 0132239_IC_Baldelomar_1900</v>
+        <v>SITE BODEGA COW</v>
       </c>
       <c r="P79" t="str">
-        <v>ICA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q79" t="str">
         <v>PROPIO</v>
@@ -4845,52 +4845,52 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="B80" t="str">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="C80" t="str">
-        <v>GL04COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D80" t="str">
-        <v>/api/evidencia/foto/7/comb-1787967626343/comb_0.jpg?v=1787967226</v>
+        <v>/api/evidencia/foto/7/comb-1788378643048/comb_0.jpg?v=1788378645</v>
       </c>
       <c r="E80" t="str">
-        <v>EMANUEL SAMUEL CONTRERAS ZEGARRA</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F80" t="str">
-        <v>2026-08-28 20:38</v>
+        <v>2026-09-02 14:50</v>
       </c>
       <c r="G80" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H80" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I80" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J80">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K80" t="str">
-        <v>CM-20260828-00000055</v>
+        <v>CM-20260829-00000043</v>
       </c>
       <c r="L80" t="str">
-        <v>N007 -00000368.</v>
+        <v>N014-00001570</v>
       </c>
       <c r="M80" t="str">
-        <v>0133756_AY_Warpapicchu</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N80" t="str">
-        <v>N007 -00000368.</v>
+        <v>N014-00001570</v>
       </c>
       <c r="O80" t="str">
-        <v>ATENCION EN SITE  DE 8 GLS RETIRADOS SE RENDIO 4 EN STOCK ESTA 4 GLS</v>
+        <v>SE CONSUMIO LOS 10 GALONES</v>
       </c>
       <c r="P80" t="str">
-        <v>AYACUCHO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q80" t="str">
         <v>PROPIO</v>
@@ -4901,22 +4901,22 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B81" t="str">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C81" t="str">
-        <v>GL02COB</v>
+        <v>GL09COB</v>
       </c>
       <c r="D81" t="str">
-        <v>/api/evidencia/foto/7/comb-1787968011783/comb_0.jpg?v=1787967609</v>
+        <v>/api/evidencia/foto/7/comb-1787668039002/comb_0.jpg?v=1787667639</v>
       </c>
       <c r="E81" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>BRIAN JESUS CABRERA ASCENCIO</v>
       </c>
       <c r="F81" t="str">
-        <v>2026-08-28 20:45</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G81" t="str">
         <v>GASTO</v>
@@ -4931,22 +4931,22 @@
         <v>0</v>
       </c>
       <c r="K81" t="str">
-        <v>CM-20260827-00000257</v>
+        <v>CM-20260824-00000197</v>
       </c>
       <c r="L81" t="str">
-        <v>N014-00001562</v>
+        <v>N024-00002842</v>
       </c>
       <c r="M81" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v>0132239_IC_Baldelomar_1900</v>
       </c>
       <c r="N81" t="str">
-        <v>N014-00001562</v>
+        <v>N024-00002842</v>
       </c>
       <c r="O81" t="str">
-        <v>SE REALIZO ABASTECIMIENTO DE 10 GLS</v>
+        <v>ATENCION CORTE PROGRAMADO AFENA ECHO POR YAIR ESCAJADILLO 0132239_IC_Baldelomar_1900</v>
       </c>
       <c r="P81" t="str">
-        <v>CHINCHA</v>
+        <v>ICA</v>
       </c>
       <c r="Q81" t="str">
         <v>PROPIO</v>
@@ -4957,52 +4957,52 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B82" t="str">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C82" t="str">
-        <v>GL12HWI</v>
+        <v>GL04COB</v>
       </c>
       <c r="D82" t="str">
-        <v>/api/evidencia/foto/7/comb-1787933956984/comb_0.jpg?v=1787933927</v>
+        <v>/api/evidencia/foto/7/comb-1787967626343/comb_0.jpg?v=1787967226</v>
       </c>
       <c r="E82" t="str">
-        <v>DINO ANTHONY QUISPE FLORES</v>
+        <v>EMANUEL SAMUEL CONTRERAS ZEGARRA</v>
       </c>
       <c r="F82" t="str">
-        <v>2026-08-28 11:15</v>
+        <v>2026-08-28 20:38</v>
       </c>
       <c r="G82" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H82" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I82" t="str">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="J82">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="K82" t="str">
-        <v>CM-20260826-00000172</v>
+        <v>CM-20260828-00000055</v>
       </c>
       <c r="L82" t="str">
-        <v>0132897</v>
+        <v>N007 -00000368.</v>
       </c>
       <c r="M82" t="str">
-        <v>0132897_PN_Repetidor_Vizcach</v>
+        <v>0133756_AY_Warpapicchu</v>
       </c>
       <c r="N82" t="str">
-        <v>N009-00000598</v>
+        <v>N007 -00000368.</v>
       </c>
       <c r="O82" t="str">
-        <v>se solicito para faena</v>
+        <v>ATENCION EN SITE  DE 8 GLS RETIRADOS SE RENDIO 4 EN STOCK ESTA 4 GLS</v>
       </c>
       <c r="P82" t="str">
-        <v>PUNO</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q82" t="str">
         <v>PROPIO</v>
@@ -5013,52 +5013,52 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B83" t="str">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C83" t="str">
-        <v>GL12HWI</v>
+        <v>GL02COB</v>
       </c>
       <c r="D83" t="str">
-        <v>/api/evidencia/foto/7/comb-1787934229982/comb_0.jpg?v=1787934196</v>
+        <v>/api/evidencia/foto/7/comb-1787968011783/comb_0.jpg?v=1787967609</v>
       </c>
       <c r="E83" t="str">
-        <v>DINO ANTHONY QUISPE FLORES</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F83" t="str">
-        <v>2026-08-28 11:22</v>
+        <v>2026-08-28 20:45</v>
       </c>
       <c r="G83" t="str">
         <v>GASTO</v>
       </c>
       <c r="H83" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I83" t="str">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K83" t="str">
-        <v>CM-20260826-00000172</v>
+        <v>CM-20260827-00000257</v>
       </c>
       <c r="L83" t="str">
-        <v>0132897</v>
+        <v>N014-00001562</v>
       </c>
       <c r="M83" t="str">
-        <v>0132897_PN_Repetidor_Vizcach</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N83" t="str">
-        <v/>
+        <v>N014-00001562</v>
       </c>
       <c r="O83" t="str">
-        <v>Sitio híbrido BB y GEE, grupo trabajo 10horas al día de forma automática.</v>
+        <v>SE REALIZO ABASTECIMIENTO DE 10 GLS</v>
       </c>
       <c r="P83" t="str">
-        <v>PUNO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q83" t="str">
         <v>PROPIO</v>
@@ -5069,52 +5069,52 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B84" t="str">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C84" t="str">
-        <v>GL02COB</v>
+        <v>GL12HWI</v>
       </c>
       <c r="D84" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787933956984/comb_0.jpg?v=1787933927</v>
       </c>
       <c r="E84" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>DINO ANTHONY QUISPE FLORES</v>
       </c>
       <c r="F84" t="str">
-        <v>2026-08-27 15:07</v>
+        <v>2026-08-28 11:15</v>
       </c>
       <c r="G84" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H84" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I84" t="str">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="J84">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="K84" t="str">
-        <v>CM-20260827-00000257</v>
+        <v>CM-20260826-00000172</v>
       </c>
       <c r="L84" t="str">
-        <v/>
+        <v>0132897</v>
       </c>
       <c r="M84" t="str">
-        <v>SITE BODEGACOW</v>
+        <v>0132897_PN_Repetidor_Vizcach</v>
       </c>
       <c r="N84" t="str">
-        <v>SE EMITE DESPUES DEL RETIRO</v>
+        <v>N009-00000598</v>
       </c>
       <c r="O84" t="str">
-        <v/>
+        <v>se solicito para faena</v>
       </c>
       <c r="P84" t="str">
-        <v>CHINCHA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q84" t="str">
         <v>PROPIO</v>
@@ -5125,52 +5125,52 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B85" t="str">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C85" t="str">
-        <v>GL02COB</v>
+        <v>GL12HWI</v>
       </c>
       <c r="D85" t="str">
-        <v>/api/evidencia/foto/7/comb-1787947738474/comb_0.jpg?v=1787947336</v>
+        <v>/api/evidencia/foto/7/comb-1787934229982/comb_0.jpg?v=1787934196</v>
       </c>
       <c r="E85" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>DINO ANTHONY QUISPE FLORES</v>
       </c>
       <c r="F85" t="str">
-        <v>2026-08-28 15:08</v>
+        <v>2026-08-28 11:22</v>
       </c>
       <c r="G85" t="str">
         <v>GASTO</v>
       </c>
       <c r="H85" t="str">
-        <v>lgutierrez</v>
+        <v>rllanos</v>
       </c>
       <c r="I85" t="str">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="J85">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K85" t="str">
-        <v>CM-20260827-00000257</v>
+        <v>CM-20260826-00000172</v>
       </c>
       <c r="L85" t="str">
-        <v>N023-00002848</v>
+        <v>0132897</v>
       </c>
       <c r="M85" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v>0132897_PN_Repetidor_Vizcach</v>
       </c>
       <c r="N85" t="str">
-        <v>N023-00002848</v>
+        <v/>
       </c>
       <c r="O85" t="str">
-        <v>ATENCION DE CORTE</v>
+        <v>Sitio híbrido BB y GEE, grupo trabajo 10horas al día de forma automática.</v>
       </c>
       <c r="P85" t="str">
-        <v>CHINCHA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q85" t="str">
         <v>PROPIO</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B86" t="str">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C86" t="str">
-        <v>GL08HWI</v>
+        <v>GL02COB</v>
       </c>
       <c r="D86" t="str">
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>MIGUEL ANGEL HINOJOSA EGOAVIL</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F86" t="str">
-        <v>2026-08-28 21:00</v>
+        <v>2026-08-27 15:07</v>
       </c>
       <c r="G86" t="str">
         <v>INGRESO</v>
@@ -5205,31 +5205,31 @@
         <v>lgutierrez</v>
       </c>
       <c r="I86" t="str">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J86">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>CM-20260827-00000257</v>
       </c>
       <c r="L86" t="str">
         <v/>
       </c>
       <c r="M86" t="str">
-        <v>0132033_JU_Cachi_Cachi</v>
+        <v>SITE BODEGACOW</v>
       </c>
       <c r="N86" t="str">
-        <v>SE EMITE CUANDO SE RETIRA</v>
+        <v>SE EMITE DESPUES DEL RETIRO</v>
       </c>
       <c r="O86" t="str">
-        <v>EL CM SE GENERA EL ISMO DIA</v>
+        <v/>
       </c>
       <c r="P86" t="str">
-        <v>HUANCAYO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q86" t="str">
-        <v>ENTEL</v>
+        <v>PROPIO</v>
       </c>
       <c r="R86" t="str">
         <v/>
@@ -5237,22 +5237,22 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B87" t="str">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C87" t="str">
-        <v>GL18COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D87" t="str">
-        <v>/api/evidencia/foto/7/90/comb_0.jpg?v=1787952076</v>
+        <v>/api/evidencia/foto/7/comb-1787947738474/comb_0.jpg?v=1787947336</v>
       </c>
       <c r="E87" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F87" t="str">
-        <v>2026-08-27 15:44</v>
+        <v>2026-08-28 15:08</v>
       </c>
       <c r="G87" t="str">
         <v>GASTO</v>
@@ -5264,25 +5264,25 @@
         <v>10</v>
       </c>
       <c r="J87">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K87" t="str">
-        <v>CM-20260827-00000115</v>
+        <v>CM-20260827-00000257</v>
       </c>
       <c r="L87" t="str">
         <v>N023-00002848</v>
       </c>
       <c r="M87" t="str">
-        <v>0131688_IC_AV_Melchorita</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N87" t="str">
-        <v>N023-00001548</v>
+        <v>N023-00002848</v>
       </c>
       <c r="O87" t="str">
-        <v>CORTE PROGRAMADO SE RETIRO COMBUSTIBLE LOS 40 GLS CON EL QRGL13  QIUE YA NO PERTENECE A ICA</v>
+        <v>ATENCION DE CORTE</v>
       </c>
       <c r="P87" t="str">
-        <v>ICA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q87" t="str">
         <v>PROPIO</v>
@@ -5293,55 +5293,55 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B88" t="str">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C88" t="str">
-        <v>GL18COB</v>
+        <v>GL08HWI</v>
       </c>
       <c r="D88" t="str">
-        <v>/api/evidencia/foto/7/comb-1787953451334/comb_0.jpg?v=1787953048</v>
+        <v/>
       </c>
       <c r="E88" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>MIGUEL ANGEL HINOJOSA EGOAVIL</v>
       </c>
       <c r="F88" t="str">
-        <v>2026-08-27 16:41</v>
+        <v>2026-08-28 21:00</v>
       </c>
       <c r="G88" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H88" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I88" t="str">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J88">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K88" t="str">
-        <v>CM-20260827-00000116</v>
+        <v/>
       </c>
       <c r="L88" t="str">
-        <v>N023-00002848</v>
+        <v/>
       </c>
       <c r="M88" t="str">
-        <v>0130831_IC_Grocio_Prado</v>
+        <v>0132033_JU_Cachi_Cachi</v>
       </c>
       <c r="N88" t="str">
-        <v>N023-00002848</v>
+        <v>SE EMITE CUANDO SE RETIRA</v>
       </c>
       <c r="O88" t="str">
-        <v>ATENCION CORTE PROGRAMADO SITE GROCIO PRADO</v>
+        <v>EL CM SE GENERA EL ISMO DIA</v>
       </c>
       <c r="P88" t="str">
-        <v>ICA</v>
+        <v>HUANCAYO</v>
       </c>
       <c r="Q88" t="str">
-        <v>PROPIO</v>
+        <v>ENTEL</v>
       </c>
       <c r="R88" t="str">
         <v/>
@@ -5349,22 +5349,22 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B89" t="str">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C89" t="str">
         <v>GL18COB</v>
       </c>
       <c r="D89" t="str">
-        <v>/api/evidencia/foto/7/comb-1787953890791/comb_0.jpg?v=1787953488</v>
+        <v>/api/evidencia/foto/7/90/comb_0.jpg?v=1787952076</v>
       </c>
       <c r="E89" t="str">
-        <v>YAIR HANS ESCAJADILLO MALLMA</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F89" t="str">
-        <v>2026-08-27 16:48</v>
+        <v>2026-08-27 15:44</v>
       </c>
       <c r="G89" t="str">
         <v>GASTO</v>
@@ -5376,22 +5376,22 @@
         <v>10</v>
       </c>
       <c r="J89">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K89" t="str">
-        <v>CM-20260827-00000102</v>
+        <v>CM-20260827-00000115</v>
       </c>
       <c r="L89" t="str">
         <v>N023-00002848</v>
       </c>
       <c r="M89" t="str">
-        <v>0132232_IC_Grocio</v>
+        <v>0131688_IC_AV_Melchorita</v>
       </c>
       <c r="N89" t="str">
-        <v>N023-00002848</v>
+        <v>N023-00001548</v>
       </c>
       <c r="O89" t="str">
-        <v>ATENCION CORTE PROGRAMADO REALIZADO X YAIR ESCAJADILLO CON QR DE EDDY GARCIA</v>
+        <v>CORTE PROGRAMADO SE RETIRO COMBUSTIBLE LOS 40 GLS CON EL QRGL13  QIUE YA NO PERTENECE A ICA</v>
       </c>
       <c r="P89" t="str">
         <v>ICA</v>
@@ -5405,52 +5405,52 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B90" t="str">
+        <v>91</v>
+      </c>
+      <c r="C90" t="str">
+        <v>GL18COB</v>
+      </c>
+      <c r="D90" t="str">
+        <v>/api/evidencia/foto/7/comb-1787953451334/comb_0.jpg?v=1787953048</v>
+      </c>
+      <c r="E90" t="str">
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+      </c>
+      <c r="F90" t="str">
+        <v>2026-08-27 16:41</v>
+      </c>
+      <c r="G90" t="str">
+        <v>GASTO</v>
+      </c>
+      <c r="H90" t="str">
+        <v>lgutierrez</v>
+      </c>
+      <c r="I90" t="str">
+        <v>10</v>
+      </c>
+      <c r="J90">
         <v>25</v>
       </c>
-      <c r="C90" t="str">
-        <v>GL11COB</v>
-      </c>
-      <c r="D90" t="str">
-        <v>/api/evidencia/foto/7/25/comb_0.jpg?v=1787608296</v>
-      </c>
-      <c r="E90" t="str">
-        <v>DINO ANTHONY QUISPE FLORES</v>
-      </c>
-      <c r="F90" t="str">
-        <v>2026-08-20 00:00</v>
-      </c>
-      <c r="G90" t="str">
-        <v>INGRESO</v>
-      </c>
-      <c r="H90" t="str">
-        <v>ygalvez</v>
-      </c>
-      <c r="I90" t="str">
-        <v>20</v>
-      </c>
-      <c r="J90">
-        <v>30</v>
-      </c>
       <c r="K90" t="str">
-        <v>CM-20260820-00000151</v>
+        <v>CM-20260827-00000116</v>
       </c>
       <c r="L90" t="str">
-        <v/>
+        <v>N023-00002848</v>
       </c>
       <c r="M90" t="str">
-        <v/>
+        <v>0130831_IC_Grocio_Prado</v>
       </c>
       <c r="N90" t="str">
-        <v>N014-00000901</v>
+        <v>N023-00002848</v>
       </c>
       <c r="O90" t="str">
-        <v>0132860_PN_El_Dorado_Puno</v>
+        <v>ATENCION CORTE PROGRAMADO SITE GROCIO PRADO</v>
       </c>
       <c r="P90" t="str">
-        <v>PUNO</v>
+        <v>ICA</v>
       </c>
       <c r="Q90" t="str">
         <v>PROPIO</v>
@@ -5461,25 +5461,25 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="B91" t="str">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="C91" t="str">
-        <v>GL02COB</v>
+        <v>GL18COB</v>
       </c>
       <c r="D91" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787953890791/comb_0.jpg?v=1787953488</v>
       </c>
       <c r="E91" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>YAIR HANS ESCAJADILLO MALLMA</v>
       </c>
       <c r="F91" t="str">
-        <v>2026-08-18 00:00</v>
+        <v>2026-08-27 16:48</v>
       </c>
       <c r="G91" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H91" t="str">
         <v>lgutierrez</v>
@@ -5488,25 +5488,25 @@
         <v>10</v>
       </c>
       <c r="J91">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K91" t="str">
-        <v>CM-20260818-00000075</v>
+        <v>CM-20260827-00000102</v>
       </c>
       <c r="L91" t="str">
-        <v/>
+        <v>N023-00002848</v>
       </c>
       <c r="M91" t="str">
-        <v/>
+        <v>0132232_IC_Grocio</v>
       </c>
       <c r="N91" t="str">
-        <v/>
+        <v>N023-00002848</v>
       </c>
       <c r="O91" t="str">
-        <v>Pendiente de subir factura</v>
+        <v>ATENCION CORTE PROGRAMADO REALIZADO X YAIR ESCAJADILLO CON QR DE EDDY GARCIA</v>
       </c>
       <c r="P91" t="str">
-        <v>CHINCHA</v>
+        <v>ICA</v>
       </c>
       <c r="Q91" t="str">
         <v>PROPIO</v>
@@ -5517,37 +5517,37 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B92" t="str">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C92" t="str">
-        <v>GL23COB</v>
+        <v>GL11COB</v>
       </c>
       <c r="D92" t="str">
-        <v>/api/evidencia/foto/7/10/comb_0.jpg?v=1787158351</v>
+        <v>/api/evidencia/foto/7/25/comb_0.jpg?v=1787608296</v>
       </c>
       <c r="E92" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>DINO ANTHONY QUISPE FLORES</v>
       </c>
       <c r="F92" t="str">
-        <v>2026-08-19 00:00</v>
+        <v>2026-08-20 00:00</v>
       </c>
       <c r="G92" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H92" t="str">
         <v>ygalvez</v>
       </c>
       <c r="I92" t="str">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K92" t="str">
-        <v>CM-20260818-00000097</v>
+        <v>CM-20260820-00000151</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -5556,13 +5556,13 @@
         <v/>
       </c>
       <c r="N92" t="str">
-        <v>N020-00003344</v>
+        <v>N014-00000901</v>
       </c>
       <c r="O92" t="str">
-        <v>RFC-20260819-0002</v>
+        <v>0132860_PN_El_Dorado_Puno</v>
       </c>
       <c r="P92" t="str">
-        <v>AREQUIPA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q92" t="str">
         <v>PROPIO</v>
@@ -5573,25 +5573,25 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B93" t="str">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C93" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D93" t="str">
-        <v>/api/evidencia/foto/7/comb-1787158108083/comb_0.jpg?v=1787157716</v>
+        <v/>
       </c>
       <c r="E93" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F93" t="str">
-        <v>2026-08-19 00:00</v>
+        <v>2026-08-18 00:00</v>
       </c>
       <c r="G93" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H93" t="str">
         <v>lgutierrez</v>
@@ -5600,7 +5600,7 @@
         <v>10</v>
       </c>
       <c r="J93">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K93" t="str">
         <v>CM-20260818-00000075</v>
@@ -5615,7 +5615,7 @@
         <v/>
       </c>
       <c r="O93" t="str">
-        <v>RFC-20260818-0040 SE  CERRO FAENA 10 GLS</v>
+        <v>Pendiente de subir factura</v>
       </c>
       <c r="P93" t="str">
         <v>CHINCHA</v>
@@ -5629,19 +5629,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B94" t="str">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C94" t="str">
-        <v>GL02COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D94" t="str">
-        <v>/api/evidencia/foto/7/comb-1787158837673/comb_0.jpg?v=1787158444</v>
+        <v>/api/evidencia/foto/7/10/comb_0.jpg?v=1787158351</v>
       </c>
       <c r="E94" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F94" t="str">
         <v>2026-08-19 00:00</v>
@@ -5650,16 +5650,16 @@
         <v>GASTO</v>
       </c>
       <c r="H94" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I94" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" t="str">
-        <v>CM-20260817-00000221</v>
+        <v>CM-20260818-00000097</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -5668,13 +5668,13 @@
         <v/>
       </c>
       <c r="N94" t="str">
-        <v/>
+        <v>N020-00003344</v>
       </c>
       <c r="O94" t="str">
-        <v>SE LIQUIDO 10 GLS IC_COW_CHINCHA</v>
+        <v>RFC-20260819-0002</v>
       </c>
       <c r="P94" t="str">
-        <v>CHINCHA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q94" t="str">
         <v>PROPIO</v>
@@ -5685,16 +5685,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B95" t="str">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C95" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D95" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787158108083/comb_0.jpg?v=1787157716</v>
       </c>
       <c r="E95" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
@@ -5703,7 +5703,7 @@
         <v>2026-08-19 00:00</v>
       </c>
       <c r="G95" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H95" t="str">
         <v>lgutierrez</v>
@@ -5715,7 +5715,7 @@
         <v>10</v>
       </c>
       <c r="K95" t="str">
-        <v>CM-20260819-00000058</v>
+        <v>CM-20260818-00000075</v>
       </c>
       <c r="L95" t="str">
         <v/>
@@ -5724,10 +5724,10 @@
         <v/>
       </c>
       <c r="N95" t="str">
-        <v>PENDIENTE SE SUBE DESPUES DE RETIRO</v>
+        <v/>
       </c>
       <c r="O95" t="str">
-        <v>CM-20260819-00000058 SITE BODEGA COW</v>
+        <v>RFC-20260818-0040 SE  CERRO FAENA 10 GLS</v>
       </c>
       <c r="P95" t="str">
         <v>CHINCHA</v>
@@ -5741,22 +5741,22 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B96" t="str">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C96" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D96" t="str">
-        <v>/api/evidencia/foto/7/comb-1787237776346/comb_0.jpg?v=1787237381</v>
+        <v>/api/evidencia/foto/7/comb-1787158837673/comb_0.jpg?v=1787158444</v>
       </c>
       <c r="E96" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F96" t="str">
-        <v>2026-08-20 00:00</v>
+        <v>2026-08-19 00:00</v>
       </c>
       <c r="G96" t="str">
         <v>GASTO</v>
@@ -5771,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="str">
-        <v>CM-20260819-00000058</v>
+        <v>CM-20260817-00000221</v>
       </c>
       <c r="L96" t="str">
         <v/>
@@ -5783,7 +5783,7 @@
         <v/>
       </c>
       <c r="O96" t="str">
-        <v>SE RINDE LOS 10 GLNS RETIRADOS PARA ATENCIÓN DE CM-20260819-0000058 PARA CONTINUAR CON EL SITE IC_BODEGA_COW.</v>
+        <v>SE LIQUIDO 10 GLS IC_COW_CHINCHA</v>
       </c>
       <c r="P96" t="str">
         <v>CHINCHA</v>
@@ -5797,19 +5797,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>10</v>
+      </c>
+      <c r="B97" t="str">
         <v>13</v>
       </c>
-      <c r="B97" t="str">
-        <v>18</v>
-      </c>
       <c r="C97" t="str">
-        <v>GL23COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D97" t="str">
-        <v>/api/evidencia/foto/7/18/comb_0.jpg?v=1787255520</v>
+        <v/>
       </c>
       <c r="E97" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F97" t="str">
         <v>2026-08-19 00:00</v>
@@ -5818,16 +5818,16 @@
         <v>INGRESO</v>
       </c>
       <c r="H97" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I97" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J97">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K97" t="str">
-        <v>CM-20260819-00000056</v>
+        <v>CM-20260819-00000058</v>
       </c>
       <c r="L97" t="str">
         <v/>
@@ -5836,13 +5836,13 @@
         <v/>
       </c>
       <c r="N97" t="str">
-        <v>N029-00001177</v>
+        <v>PENDIENTE SE SUBE DESPUES DE RETIRO</v>
       </c>
       <c r="O97" t="str">
-        <v>0134389EL_CARMEN_AQP corte de energía</v>
+        <v>CM-20260819-00000058 SITE BODEGA COW</v>
       </c>
       <c r="P97" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q97" t="str">
         <v>PROPIO</v>
@@ -5853,19 +5853,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B98" t="str">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C98" t="str">
-        <v>GL04COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D98" t="str">
-        <v>/api/evidencia/foto/7/comb-1787238343340/comb_0.jpg?v=1787237948</v>
+        <v>/api/evidencia/foto/7/comb-1787237776346/comb_0.jpg?v=1787237381</v>
       </c>
       <c r="E98" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F98" t="str">
         <v>2026-08-20 00:00</v>
@@ -5877,13 +5877,13 @@
         <v>lgutierrez</v>
       </c>
       <c r="I98" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J98">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K98" t="str">
-        <v>CM-20260819-00000169</v>
+        <v>CM-20260819-00000058</v>
       </c>
       <c r="L98" t="str">
         <v/>
@@ -5895,10 +5895,10 @@
         <v/>
       </c>
       <c r="O98" t="str">
-        <v>ATENCION SITE 0133760_AY_Quinua PRIORIDAD  P4</v>
+        <v>SE RINDE LOS 10 GLNS RETIRADOS PARA ATENCIÓN DE CM-20260819-0000058 PARA CONTINUAR CON EL SITE IC_BODEGA_COW.</v>
       </c>
       <c r="P98" t="str">
-        <v>AYACUCHO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q98" t="str">
         <v>PROPIO</v>
@@ -5909,25 +5909,25 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
+        <v>13</v>
+      </c>
+      <c r="B99" t="str">
         <v>18</v>
-      </c>
-      <c r="B99" t="str">
-        <v>22</v>
       </c>
       <c r="C99" t="str">
         <v>GL23COB</v>
       </c>
       <c r="D99" t="str">
-        <v>/api/evidencia/foto/7/comb-1787256413970/comb_0.jpg?v=1787256414</v>
+        <v>/api/evidencia/foto/7/18/comb_0.jpg?v=1787255520</v>
       </c>
       <c r="E99" t="str">
         <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F99" t="str">
-        <v>2026-08-20 00:00</v>
+        <v>2026-08-19 00:00</v>
       </c>
       <c r="G99" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H99" t="str">
         <v>ygalvez</v>
@@ -5936,7 +5936,7 @@
         <v>9</v>
       </c>
       <c r="J99">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K99" t="str">
         <v>CM-20260819-00000056</v>
@@ -5948,10 +5948,10 @@
         <v/>
       </c>
       <c r="N99" t="str">
-        <v/>
+        <v>N029-00001177</v>
       </c>
       <c r="O99" t="str">
-        <v>RFC-20260820-0001 0134389_AQ_El_Carmen_AQP se abastecio 9gl</v>
+        <v>0134389EL_CARMEN_AQP corte de energía</v>
       </c>
       <c r="P99" t="str">
         <v>AREQUIPA</v>
@@ -5965,37 +5965,37 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B100" t="str">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C100" t="str">
-        <v>GL07COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D100" t="str">
-        <v>/api/evidencia/foto/7/27/comb_0.jpg?v=1787346928</v>
+        <v>/api/evidencia/foto/7/comb-1787238343340/comb_0.jpg?v=1787237948</v>
       </c>
       <c r="E100" t="str">
-        <v>JOSE MIGUEL NINA ESQUIA</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F100" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-08-20 00:00</v>
       </c>
       <c r="G100" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H100" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I100" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J100">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K100" t="str">
-        <v>CM-20260821-00000127</v>
+        <v>CM-20260819-00000169</v>
       </c>
       <c r="L100" t="str">
         <v/>
@@ -6004,13 +6004,13 @@
         <v/>
       </c>
       <c r="N100" t="str">
-        <v>N034-00000377</v>
+        <v/>
       </c>
       <c r="O100" t="str">
-        <v>0132601_TA_La_Yarada</v>
+        <v>ATENCION SITE 0133760_AY_Quinua PRIORIDAD  P4</v>
       </c>
       <c r="P100" t="str">
-        <v>TACNA</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q100" t="str">
         <v>PROPIO</v>
@@ -6021,37 +6021,37 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B101" t="str">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C101" t="str">
-        <v>GL04COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D101" t="str">
-        <v>/api/evidencia/foto/7/comb-1787345220888/comb_0.jpg?v=1787344825</v>
+        <v>/api/evidencia/foto/7/comb-1787256413970/comb_0.jpg?v=1787256414</v>
       </c>
       <c r="E101" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F101" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-08-20 00:00</v>
       </c>
       <c r="G101" t="str">
         <v>GASTO</v>
       </c>
       <c r="H101" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I101" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J101">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K101" t="str">
-        <v>CM-20260821-00000090</v>
+        <v>CM-20260819-00000056</v>
       </c>
       <c r="L101" t="str">
         <v/>
@@ -6060,13 +6060,13 @@
         <v/>
       </c>
       <c r="N101" t="str">
-        <v>N007-00000356</v>
+        <v/>
       </c>
       <c r="O101" t="str">
-        <v>CM-20260821-00000090   CM-20260821-00000090     0133740 SITE AY_TERMINAL_TERRESTRE</v>
+        <v>RFC-20260820-0001 0134389_AQ_El_Carmen_AQP se abastecio 9gl</v>
       </c>
       <c r="P101" t="str">
-        <v>AYACUCHO</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q101" t="str">
         <v>PROPIO</v>
@@ -6077,19 +6077,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B102" t="str">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C102" t="str">
-        <v>GL04COB</v>
+        <v>GL07COB</v>
       </c>
       <c r="D102" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/27/comb_0.jpg?v=1787346928</v>
       </c>
       <c r="E102" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>JOSE MIGUEL NINA ESQUIA</v>
       </c>
       <c r="F102" t="str">
         <v>2026-08-21 00:00</v>
@@ -6098,16 +6098,16 @@
         <v>INGRESO</v>
       </c>
       <c r="H102" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I102" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J102">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K102" t="str">
-        <v>CM-20260821-00000231</v>
+        <v>CM-20260821-00000127</v>
       </c>
       <c r="L102" t="str">
         <v/>
@@ -6116,13 +6116,13 @@
         <v/>
       </c>
       <c r="N102" t="str">
-        <v>SE EMITE DESPUES DE RETIRO</v>
+        <v>N034-00000377</v>
       </c>
       <c r="O102" t="str">
-        <v/>
+        <v>0132601_TA_La_Yarada</v>
       </c>
       <c r="P102" t="str">
-        <v>AYACUCHO</v>
+        <v>TACNA</v>
       </c>
       <c r="Q102" t="str">
         <v>PROPIO</v>
@@ -6133,19 +6133,19 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B103" t="str">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C103" t="str">
-        <v>GL22COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D103" t="str">
-        <v>/api/evidencia/foto/7/comb-1787348728483/comb_0.jpg?v=1787348734</v>
+        <v>/api/evidencia/foto/7/comb-1787345220888/comb_0.jpg?v=1787344825</v>
       </c>
       <c r="E103" t="str">
-        <v>ALEX DOMINGO ALVAREZ PUMA</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F103" t="str">
         <v>2026-08-21 00:00</v>
@@ -6154,31 +6154,31 @@
         <v>GASTO</v>
       </c>
       <c r="H103" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I103" t="str">
+        <v>6</v>
+      </c>
+      <c r="J103">
         <v>4</v>
       </c>
-      <c r="J103">
-        <v>5</v>
-      </c>
       <c r="K103" t="str">
-        <v>CM-20260820-00000098</v>
+        <v>CM-20260821-00000090</v>
       </c>
       <c r="L103" t="str">
-        <v>RFC-20260820-0010</v>
+        <v/>
       </c>
       <c r="M103" t="str">
         <v/>
       </c>
       <c r="N103" t="str">
-        <v/>
+        <v>N007-00000356</v>
       </c>
       <c r="O103" t="str">
-        <v>site 0132755_CS_Huancarani solo se consume 4 de N024-00000092</v>
+        <v>CM-20260821-00000090   CM-20260821-00000090     0133740 SITE AY_TERMINAL_TERRESTRE</v>
       </c>
       <c r="P103" t="str">
-        <v>CUZCO</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q103" t="str">
         <v>PROPIO</v>
@@ -6189,52 +6189,52 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B104" t="str">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C104" t="str">
-        <v>GL02COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D104" t="str">
-        <v>/api/evidencia/foto/7/comb-1787360975718/comb_0.jpg?v=1787360580</v>
+        <v/>
       </c>
       <c r="E104" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F104" t="str">
         <v>2026-08-21 00:00</v>
       </c>
       <c r="G104" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H104" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I104" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J104">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K104" t="str">
-        <v>CM-20260820-00000060</v>
+        <v>CM-20260821-00000231</v>
       </c>
       <c r="L104" t="str">
-        <v>N014 00001504</v>
+        <v/>
       </c>
       <c r="M104" t="str">
         <v/>
       </c>
       <c r="N104" t="str">
-        <v/>
+        <v>SE EMITE DESPUES DE RETIRO</v>
       </c>
       <c r="O104" t="str">
-        <v>SE ABSTECIO 10 GLS PARA SITE BODEGA</v>
+        <v/>
       </c>
       <c r="P104" t="str">
-        <v>CHINCHA</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q104" t="str">
         <v>PROPIO</v>
@@ -6245,52 +6245,52 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B105" t="str">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C105" t="str">
-        <v>GL09COB</v>
+        <v>GL22COB</v>
       </c>
       <c r="D105" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787348728483/comb_0.jpg?v=1787348734</v>
       </c>
       <c r="E105" t="str">
-        <v>BRIAN JESUS CABRERA ASCENCIO</v>
+        <v>ALEX DOMINGO ALVAREZ PUMA</v>
       </c>
       <c r="F105" t="str">
-        <v>2026-08-22 00:00</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G105" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H105" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I105" t="str">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="J105">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>CM-20260820-00000098</v>
       </c>
       <c r="L105" t="str">
-        <v/>
+        <v>RFC-20260820-0010</v>
       </c>
       <c r="M105" t="str">
         <v/>
       </c>
       <c r="N105" t="str">
-        <v>SE EMITE CUANDO SE RETIRE</v>
+        <v/>
       </c>
       <c r="O105" t="str">
-        <v>CORTE PROGRAMADO JOSÉ MIRANDA, VICTORIA PISCO,IDELFONSO LIRA,CLAVELLES</v>
+        <v>site 0132755_CS_Huancarani solo se consume 4 de N024-00000092</v>
       </c>
       <c r="P105" t="str">
-        <v>ICA</v>
+        <v>CUZCO</v>
       </c>
       <c r="Q105" t="str">
         <v>PROPIO</v>
@@ -6301,49 +6301,49 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
+        <v>30</v>
+      </c>
+      <c r="B106" t="str">
         <v>35</v>
-      </c>
-      <c r="B106" t="str">
-        <v>38</v>
       </c>
       <c r="C106" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D106" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787360975718/comb_0.jpg?v=1787360580</v>
       </c>
       <c r="E106" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F106" t="str">
-        <v>2026-08-22 00:00</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G106" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H106" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I106" t="str">
+        <v>10</v>
+      </c>
+      <c r="J106">
         <v>20</v>
       </c>
-      <c r="J106">
-        <v>40</v>
-      </c>
       <c r="K106" t="str">
-        <v/>
+        <v>CM-20260820-00000060</v>
       </c>
       <c r="L106" t="str">
-        <v/>
+        <v>N014 00001504</v>
       </c>
       <c r="M106" t="str">
         <v/>
       </c>
       <c r="N106" t="str">
-        <v>SE EMITE AL RETIRAR</v>
+        <v/>
       </c>
       <c r="O106" t="str">
-        <v>CORTE PROGRAMADO Site: IC_SAN_CLEMENTE</v>
+        <v>SE ABSTECIO 10 GLS PARA SITE BODEGA</v>
       </c>
       <c r="P106" t="str">
         <v>CHINCHA</v>
@@ -6357,22 +6357,22 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B107" t="str">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C107" t="str">
-        <v>GL02COB</v>
+        <v>GL09COB</v>
       </c>
       <c r="D107" t="str">
         <v/>
       </c>
       <c r="E107" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>BRIAN JESUS CABRERA ASCENCIO</v>
       </c>
       <c r="F107" t="str">
-        <v>2026-08-23 00:00</v>
+        <v>2026-08-22 00:00</v>
       </c>
       <c r="G107" t="str">
         <v>INGRESO</v>
@@ -6381,13 +6381,13 @@
         <v>lgutierrez</v>
       </c>
       <c r="I107" t="str">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J107">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K107" t="str">
-        <v>CM-20260822-00000057</v>
+        <v/>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -6396,13 +6396,13 @@
         <v/>
       </c>
       <c r="N107" t="str">
-        <v>AE EMITE CUANTO SE RETIRE COMBUSTIBLE</v>
+        <v>SE EMITE CUANDO SE RETIRE</v>
       </c>
       <c r="O107" t="str">
-        <v>IC_BODEGA_COW</v>
+        <v>CORTE PROGRAMADO JOSÉ MIRANDA, VICTORIA PISCO,IDELFONSO LIRA,CLAVELLES</v>
       </c>
       <c r="P107" t="str">
-        <v>CHINCHA</v>
+        <v>ICA</v>
       </c>
       <c r="Q107" t="str">
         <v>PROPIO</v>
@@ -6413,37 +6413,37 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B108" t="str">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C108" t="str">
-        <v>GL17COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D108" t="str">
-        <v>/api/evidencia/foto/7/comb-1787585042393/comb_0.jpg?v=1787585044</v>
+        <v/>
       </c>
       <c r="E108" t="str">
-        <v>VICTOR IGNACIO ORTEGA ALAVE</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F108" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-22 00:00</v>
       </c>
       <c r="G108" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H108" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I108" t="str">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J108">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K108" t="str">
-        <v>CM-20260823-00000230</v>
+        <v/>
       </c>
       <c r="L108" t="str">
         <v/>
@@ -6452,13 +6452,13 @@
         <v/>
       </c>
       <c r="N108" t="str">
-        <v>N020-00003415</v>
+        <v>SE EMITE AL RETIRAR</v>
       </c>
       <c r="O108" t="str">
-        <v>0132370_AQ_Camilo_Joya</v>
+        <v>CORTE PROGRAMADO Site: IC_SAN_CLEMENTE</v>
       </c>
       <c r="P108" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q108" t="str">
         <v>PROPIO</v>
@@ -6469,37 +6469,37 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B109" t="str">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C109" t="str">
-        <v>GL11COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D109" t="str">
-        <v>/api/evidencia/foto/7/comb-1787590818697/comb_0.jpg?v=1787590822</v>
+        <v/>
       </c>
       <c r="E109" t="str">
-        <v>ABEL JOHN CHIRINOS CHINO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F109" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-23 00:00</v>
       </c>
       <c r="G109" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H109" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I109" t="str">
         <v>10</v>
       </c>
       <c r="J109">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K109" t="str">
-        <v>CM-20260823-00000377</v>
+        <v>CM-20260822-00000057</v>
       </c>
       <c r="L109" t="str">
         <v/>
@@ -6508,13 +6508,13 @@
         <v/>
       </c>
       <c r="N109" t="str">
-        <v>N005-00000955</v>
+        <v>AE EMITE CUANTO SE RETIRE COMBUSTIBLE</v>
       </c>
       <c r="O109" t="str">
-        <v>0132817_PN_Boris_Suas</v>
+        <v>IC_BODEGA_COW</v>
       </c>
       <c r="P109" t="str">
-        <v>PUNO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q109" t="str">
         <v>PROPIO</v>
@@ -6525,52 +6525,52 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B110" t="str">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C110" t="str">
-        <v>GL18COB</v>
+        <v>GL17COB</v>
       </c>
       <c r="D110" t="str">
-        <v>/api/evidencia/foto/7/comb-1787673177151/comb_0.jpg?v=1787672777</v>
+        <v>/api/evidencia/foto/7/comb-1787585042393/comb_0.jpg?v=1787585044</v>
       </c>
       <c r="E110" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>VICTOR IGNACIO ORTEGA ALAVE</v>
       </c>
       <c r="F110" t="str">
         <v>2026-08-24 00:00</v>
       </c>
       <c r="G110" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H110" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I110" t="str">
         <v>10</v>
       </c>
       <c r="J110">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K110" t="str">
-        <v>CM-20260823-00000398</v>
+        <v>CM-20260823-00000230</v>
       </c>
       <c r="L110" t="str">
-        <v>N024-00002843</v>
+        <v/>
       </c>
       <c r="M110" t="str">
-        <v>SITE 013210705_IC_Aeropuerto_Pisco</v>
+        <v/>
       </c>
       <c r="N110" t="str">
-        <v>N024-00002843</v>
+        <v>N020-00003415</v>
       </c>
       <c r="O110" t="str">
-        <v>CORTE PROGRAMADO SITE 013210705_IC_Aeropuerto_Pisco /</v>
+        <v>0132370_AQ_Camilo_Joya</v>
       </c>
       <c r="P110" t="str">
-        <v>ICA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q110" t="str">
         <v>PROPIO</v>
@@ -6581,52 +6581,52 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="B111" t="str">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C111" t="str">
-        <v>GL17COB</v>
+        <v>GL11COB</v>
       </c>
       <c r="D111" t="str">
-        <v>/api/evidencia/foto/7/comb-1787673879144/comb_0.jpg?v=1787673880</v>
+        <v>/api/evidencia/foto/7/comb-1787590818697/comb_0.jpg?v=1787590822</v>
       </c>
       <c r="E111" t="str">
-        <v>VICTOR IGNACIO ORTEGA ALAVE</v>
+        <v>ABEL JOHN CHIRINOS CHINO</v>
       </c>
       <c r="F111" t="str">
-        <v>2026-08-25 00:00</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G111" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H111" t="str">
         <v>ygalvez</v>
       </c>
       <c r="I111" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J111">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K111" t="str">
-        <v>CM-20260823-00000230</v>
+        <v>CM-20260823-00000377</v>
       </c>
       <c r="L111" t="str">
-        <v>RFC-20260824-0013</v>
+        <v/>
       </c>
       <c r="M111" t="str">
         <v/>
       </c>
       <c r="N111" t="str">
-        <v/>
+        <v>N005-00000955</v>
       </c>
       <c r="O111" t="str">
-        <v>0132370_AQ_Camilo_Joya N020-00003415 se consume 2gl</v>
+        <v>0132817_PN_Boris_Suas</v>
       </c>
       <c r="P111" t="str">
-        <v>AREQUIPA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q111" t="str">
         <v>PROPIO</v>
@@ -6637,19 +6637,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B112" t="str">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C112" t="str">
-        <v>GL02COB</v>
+        <v>GL18COB</v>
       </c>
       <c r="D112" t="str">
-        <v>/api/evidencia/foto/7/comb-1787681287434/comb_0.jpg?v=1787680887</v>
+        <v>/api/evidencia/foto/7/comb-1787673177151/comb_0.jpg?v=1787672777</v>
       </c>
       <c r="E112" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F112" t="str">
         <v>2026-08-24 00:00</v>
@@ -6664,25 +6664,25 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K112" t="str">
-        <v>CM-20260822-00000057</v>
+        <v>CM-20260823-00000398</v>
       </c>
       <c r="L112" t="str">
-        <v/>
+        <v>N024-00002843</v>
       </c>
       <c r="M112" t="str">
-        <v>BODEGA COW</v>
+        <v>SITE 013210705_IC_Aeropuerto_Pisco</v>
       </c>
       <c r="N112" t="str">
-        <v>N014-00001531</v>
+        <v>N024-00002843</v>
       </c>
       <c r="O112" t="str">
-        <v>ATENCION BODEGA COW</v>
+        <v>CORTE PROGRAMADO SITE 013210705_IC_Aeropuerto_Pisco /</v>
       </c>
       <c r="P112" t="str">
-        <v>CHINCHA</v>
+        <v>ICA</v>
       </c>
       <c r="Q112" t="str">
         <v>PROPIO</v>
@@ -6693,19 +6693,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B113" t="str">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C113" t="str">
         <v>GL17COB</v>
       </c>
       <c r="D113" t="str">
-        <v>/api/evidencia/foto/7/comb-1787702956135/comb_0.jpg?v=1787702957</v>
+        <v>/api/evidencia/foto/7/comb-1787673879144/comb_0.jpg?v=1787673880</v>
       </c>
       <c r="E113" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>VICTOR IGNACIO ORTEGA ALAVE</v>
       </c>
       <c r="F113" t="str">
         <v>2026-08-25 00:00</v>
@@ -6717,16 +6717,16 @@
         <v>ygalvez</v>
       </c>
       <c r="I113" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J113">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K113" t="str">
-        <v>CM-20260825-00000114</v>
+        <v>CM-20260823-00000230</v>
       </c>
       <c r="L113" t="str">
-        <v>RFC-20260825-0018</v>
+        <v>RFC-20260824-0013</v>
       </c>
       <c r="M113" t="str">
         <v/>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="O113" t="str">
-        <v>013141788_AQ_RosarioApipa N029-00001224 solo 5gl</v>
+        <v>0132370_AQ_Camilo_Joya N020-00003415 se consume 2gl</v>
       </c>
       <c r="P113" t="str">
         <v>AREQUIPA</v>
@@ -6749,52 +6749,52 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B114" t="str">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C114" t="str">
-        <v>GL19COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D114" t="str">
-        <v>/api/evidencia/foto/7/comb-1787703632072/comb_0.jpg?v=1787703634</v>
+        <v>/api/evidencia/foto/7/comb-1787681287434/comb_0.jpg?v=1787680887</v>
       </c>
       <c r="E114" t="str">
-        <v>MOISES ANGEL AYÑAYANQUI RIOS</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F114" t="str">
-        <v>2026-08-25 00:00</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G114" t="str">
         <v>GASTO</v>
       </c>
       <c r="H114" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I114" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J114">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K114" t="str">
-        <v>CM-20260825-00000084</v>
+        <v>CM-20260822-00000057</v>
       </c>
       <c r="L114" t="str">
-        <v>RFC-20260825-0033</v>
+        <v/>
       </c>
       <c r="M114" t="str">
-        <v/>
+        <v>BODEGA COW</v>
       </c>
       <c r="N114" t="str">
-        <v/>
+        <v>N014-00001531</v>
       </c>
       <c r="O114" t="str">
-        <v>0130938_AQ_Chala N331-00031308 se consumio 8gl</v>
+        <v>ATENCION BODEGA COW</v>
       </c>
       <c r="P114" t="str">
-        <v>CAMANA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q114" t="str">
         <v>PROPIO</v>
@@ -6805,19 +6805,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B115" t="str">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C115" t="str">
-        <v>GL23COB</v>
+        <v>GL17COB</v>
       </c>
       <c r="D115" t="str">
-        <v>/api/evidencia/foto/7/comb-1787703888072/comb_0.jpg?v=1787703889</v>
+        <v>/api/evidencia/foto/7/comb-1787702956135/comb_0.jpg?v=1787702957</v>
       </c>
       <c r="E115" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F115" t="str">
         <v>2026-08-25 00:00</v>
@@ -6829,16 +6829,16 @@
         <v>ygalvez</v>
       </c>
       <c r="I115" t="str">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J115">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="K115" t="str">
-        <v>CM-20260825-00000111</v>
+        <v>CM-20260825-00000114</v>
       </c>
       <c r="L115" t="str">
-        <v>RFC-20260825-0035</v>
+        <v>RFC-20260825-0018</v>
       </c>
       <c r="M115" t="str">
         <v/>
@@ -6847,7 +6847,7 @@
         <v/>
       </c>
       <c r="O115" t="str">
-        <v>013140333_AQ_Horeb N025-00006024 solo uso 2.5gl</v>
+        <v>013141788_AQ_RosarioApipa N029-00001224 solo 5gl</v>
       </c>
       <c r="P115" t="str">
         <v>AREQUIPA</v>
@@ -6861,52 +6861,52 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B116" t="str">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C116" t="str">
-        <v>GL02COB</v>
+        <v>GL19COB</v>
       </c>
       <c r="D116" t="str">
-        <v>/api/evidencia/foto/7/comb-1787705512297/comb_0.jpg?v=1787705112</v>
+        <v>/api/evidencia/foto/7/comb-1787703632072/comb_0.jpg?v=1787703634</v>
       </c>
       <c r="E116" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MOISES ANGEL AYÑAYANQUI RIOS</v>
       </c>
       <c r="F116" t="str">
-        <v>2026-08-26 00:00</v>
+        <v>2026-08-25 00:00</v>
       </c>
       <c r="G116" t="str">
         <v>GASTO</v>
       </c>
       <c r="H116" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I116" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J116">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K116" t="str">
-        <v>CM-20260825-00000050</v>
+        <v>CM-20260825-00000084</v>
       </c>
       <c r="L116" t="str">
-        <v>N014-00001438</v>
+        <v>RFC-20260825-0033</v>
       </c>
       <c r="M116" t="str">
-        <v>BODEGACOW</v>
+        <v/>
       </c>
       <c r="N116" t="str">
-        <v>N014-00001438</v>
+        <v/>
       </c>
       <c r="O116" t="str">
-        <v>ATENCIO SITE NBODEGA COW</v>
+        <v>0130938_AQ_Chala N331-00031308 se consumio 8gl</v>
       </c>
       <c r="P116" t="str">
-        <v>CHINCHA</v>
+        <v>CAMANA</v>
       </c>
       <c r="Q116" t="str">
         <v>PROPIO</v>
@@ -6917,52 +6917,52 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B117" t="str">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C117" t="str">
-        <v>GL02COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D117" t="str">
-        <v>/api/evidencia/foto/7/comb-1787705512297/comb_0.jpg?v=1787705112</v>
+        <v>/api/evidencia/foto/7/comb-1787703888072/comb_0.jpg?v=1787703889</v>
       </c>
       <c r="E117" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F117" t="str">
-        <v>2026-08-26 00:00</v>
+        <v>2026-08-25 00:00</v>
       </c>
       <c r="G117" t="str">
         <v>GASTO</v>
       </c>
       <c r="H117" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I117" t="str">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="J117">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="K117" t="str">
-        <v>CM-20260825-00000050</v>
+        <v>CM-20260825-00000111</v>
       </c>
       <c r="L117" t="str">
-        <v>N014-00001438</v>
+        <v>RFC-20260825-0035</v>
       </c>
       <c r="M117" t="str">
         <v/>
       </c>
       <c r="N117" t="str">
-        <v>N014-000011541</v>
+        <v/>
       </c>
       <c r="O117" t="str">
-        <v>ATENCIO SITE NBODEGA COW</v>
+        <v>013140333_AQ_Horeb N025-00006024 solo uso 2.5gl</v>
       </c>
       <c r="P117" t="str">
-        <v>CHINCHA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q117" t="str">
         <v>PROPIO</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B118" t="str">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C118" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D118" t="str">
-        <v>/api/evidencia/foto/7/comb-1787785823600/comb_0.jpg?v=1787785423</v>
+        <v>/api/evidencia/foto/7/comb-1787705512297/comb_0.jpg?v=1787705112</v>
       </c>
       <c r="E118" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F118" t="str">
-        <v>2026-08-26 18:09</v>
+        <v>2026-08-26 00:00</v>
       </c>
       <c r="G118" t="str">
         <v>GASTO</v>
@@ -7000,22 +7000,22 @@
         <v>10</v>
       </c>
       <c r="J118">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K118" t="str">
         <v>CM-20260825-00000050</v>
       </c>
       <c r="L118" t="str">
-        <v>N014-00001550</v>
+        <v>N014-00001438</v>
       </c>
       <c r="M118" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v>BODEGACOW</v>
       </c>
       <c r="N118" t="str">
-        <v>N014-00001550</v>
+        <v>N014-00001438</v>
       </c>
       <c r="O118" t="str">
-        <v>ATENCION SITE  0133243_IC_Bodega_COW   N014-00001550</v>
+        <v>ATENCIO SITE NBODEGA COW</v>
       </c>
       <c r="P118" t="str">
         <v>CHINCHA</v>
@@ -7029,52 +7029,52 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B119" t="str">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C119" t="str">
-        <v>GL03COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D119" t="str">
-        <v>/api/evidencia/foto/7/comb-1787786282287/comb_0.jpg?v=1787785881</v>
+        <v>/api/evidencia/foto/7/comb-1787705512297/comb_0.jpg?v=1787705112</v>
       </c>
       <c r="E119" t="str">
-        <v>MIGUEL ANGEL HINOJOSA EGOAVIL</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F119" t="str">
-        <v>2026-08-24 18:14</v>
+        <v>2026-08-26 00:00</v>
       </c>
       <c r="G119" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H119" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I119" t="str">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J119">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K119" t="str">
-        <v>CM-20260825-00000172</v>
+        <v>CM-20260825-00000050</v>
       </c>
       <c r="L119" t="str">
-        <v>SE EMITE DESPUES</v>
+        <v>N014-00001438</v>
       </c>
       <c r="M119" t="str">
-        <v>0133945_JU_Mina_Ariana</v>
+        <v/>
       </c>
       <c r="N119" t="str">
-        <v>N003-00002502</v>
+        <v>N014-000011541</v>
       </c>
       <c r="O119" t="str">
-        <v>GEE ESTA EN MAL ESTADO SITE 0133945_JU_Mina_Ariana    N003-00002502</v>
+        <v>ATENCIO SITE NBODEGA COW</v>
       </c>
       <c r="P119" t="str">
-        <v>HUANCAYO</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q119" t="str">
         <v>PROPIO</v>
@@ -7085,52 +7085,52 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B120" t="str">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C120" t="str">
-        <v>GL18COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D120" t="str">
-        <v>/api/evidencia/foto/7/89/comb_0.jpg?v=1787949535</v>
+        <v>/api/evidencia/foto/7/comb-1787785823600/comb_0.jpg?v=1787785423</v>
       </c>
       <c r="E120" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F120" t="str">
-        <v>2026-08-28 15:13</v>
+        <v>2026-08-26 18:09</v>
       </c>
       <c r="G120" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H120" t="str">
-        <v>rllanos</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I120" t="str">
         <v>10</v>
       </c>
       <c r="J120">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K120" t="str">
-        <v>CM-20260828-00000121</v>
+        <v>CM-20260825-00000050</v>
       </c>
       <c r="L120" t="str">
-        <v>se emite en el ingreso</v>
+        <v>N014-00001550</v>
       </c>
       <c r="M120" t="str">
-        <v>0130840_IC_Rep_Marcona</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N120" t="str">
-        <v>se emite en el ingreso</v>
+        <v>N014-00001550</v>
       </c>
       <c r="O120" t="str">
-        <v>se emite factura al cierre de actividad</v>
+        <v>ATENCION SITE  0133243_IC_Bodega_COW   N014-00001550</v>
       </c>
       <c r="P120" t="str">
-        <v>ICA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q120" t="str">
         <v>PROPIO</v>
@@ -7141,52 +7141,52 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B121" t="str">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C121" t="str">
-        <v>GL11COB</v>
+        <v>GL03COB</v>
       </c>
       <c r="D121" t="str">
-        <v>/api/evidencia/foto/7/comb-1787954813061/comb_0.jpg?v=1787954813</v>
+        <v>/api/evidencia/foto/7/comb-1787786282287/comb_0.jpg?v=1787785881</v>
       </c>
       <c r="E121" t="str">
-        <v>DINO ANTHONY QUISPE FLORES</v>
+        <v>MIGUEL ANGEL HINOJOSA EGOAVIL</v>
       </c>
       <c r="F121" t="str">
-        <v>2026-08-27 16:58</v>
+        <v>2026-08-24 18:14</v>
       </c>
       <c r="G121" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H121" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I121" t="str">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J121">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K121" t="str">
-        <v>CM-20260826-00000222</v>
+        <v>CM-20260825-00000172</v>
       </c>
       <c r="L121" t="str">
-        <v>RFC-20260827-0001</v>
+        <v>SE EMITE DESPUES</v>
       </c>
       <c r="M121" t="str">
-        <v>0132858_PN_Ananea</v>
+        <v>0133945_JU_Mina_Ariana</v>
       </c>
       <c r="N121" t="str">
-        <v>N014-00000901</v>
+        <v>N003-00002502</v>
       </c>
       <c r="O121" t="str">
-        <v>faena liquidada por Marco Soto 10gl N014-00000901</v>
+        <v>GEE ESTA EN MAL ESTADO SITE 0133945_JU_Mina_Ariana    N003-00002502</v>
       </c>
       <c r="P121" t="str">
-        <v>PUNO</v>
+        <v>HUANCAYO</v>
       </c>
       <c r="Q121" t="str">
         <v>PROPIO</v>
@@ -7197,52 +7197,52 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B122" t="str">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C122" t="str">
-        <v>GL23COB</v>
+        <v>GL18COB</v>
       </c>
       <c r="D122" t="str">
-        <v>/api/evidencia/foto/7/comb-1788039999519/comb_0.jpg?v=1788040001</v>
+        <v>/api/evidencia/foto/7/89/comb_0.jpg?v=1787949535</v>
       </c>
       <c r="E122" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
       </c>
       <c r="F122" t="str">
-        <v>2026-08-29 16:44</v>
+        <v>2026-08-28 15:13</v>
       </c>
       <c r="G122" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H122" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I122" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J122">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="K122" t="str">
-        <v>CM-20260829-00000025</v>
+        <v>CM-20260828-00000121</v>
       </c>
       <c r="L122" t="str">
-        <v/>
+        <v>se emite en el ingreso</v>
       </c>
       <c r="M122" t="str">
-        <v>0134048_AQ_Punta_De_Bombon</v>
+        <v>0130840_IC_Rep_Marcona</v>
       </c>
       <c r="N122" t="str">
-        <v>N020-00003521</v>
+        <v>se emite en el ingreso</v>
       </c>
       <c r="O122" t="str">
-        <v>Retira 5gl</v>
+        <v>se emite factura al cierre de actividad</v>
       </c>
       <c r="P122" t="str">
-        <v>AREQUIPA</v>
+        <v>ICA</v>
       </c>
       <c r="Q122" t="str">
         <v>PROPIO</v>
@@ -7253,52 +7253,52 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
+        <v>82</v>
+      </c>
+      <c r="B123" t="str">
         <v>94</v>
       </c>
-      <c r="B123" t="str">
-        <v>100</v>
-      </c>
       <c r="C123" t="str">
-        <v>GL15COB</v>
+        <v>GL11COB</v>
       </c>
       <c r="D123" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787954813061/comb_0.jpg?v=1787954813</v>
       </c>
       <c r="E123" t="str">
-        <v>ELMER FLAVIANO CUBA ALVARADO</v>
+        <v>DINO ANTHONY QUISPE FLORES</v>
       </c>
       <c r="F123" t="str">
-        <v>2026-08-29 12:34</v>
+        <v>2026-08-27 16:58</v>
       </c>
       <c r="G123" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H123" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I123" t="str">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J123">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K123" t="str">
-        <v/>
+        <v>CM-20260826-00000222</v>
       </c>
       <c r="L123" t="str">
-        <v>se adjunta al termino de la faena</v>
+        <v>RFC-20260827-0001</v>
       </c>
       <c r="M123" t="str">
-        <v>0133543_LH_Mapresa</v>
+        <v>0132858_PN_Ananea</v>
       </c>
       <c r="N123" t="str">
-        <v>se adjunta al termino de la faena</v>
+        <v>N014-00000901</v>
       </c>
       <c r="O123" t="str">
-        <v>Site: LH_DIVISORIA, LH_ALOMIAS, LH_MICROCUENCA TULUMAYO, LH_MAPRESA, LH_SAN JORGE</v>
+        <v>faena liquidada por Marco Soto 10gl N014-00000901</v>
       </c>
       <c r="P123" t="str">
-        <v>HUANUCO-CERRO PASCO</v>
+        <v>PUNO</v>
       </c>
       <c r="Q123" t="str">
         <v>PROPIO</v>
@@ -7309,22 +7309,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B124" t="str">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C124" t="str">
-        <v>GL07COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D124" t="str">
-        <v>/api/evidencia/foto/7/comb-1788048390431/comb_0.jpg?v=1788048393</v>
+        <v>/api/evidencia/foto/7/comb-1788039999519/comb_0.jpg?v=1788040001</v>
       </c>
       <c r="E124" t="str">
-        <v>JOSE MIGUEL NINA ESQUIA</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F124" t="str">
-        <v>2026-08-16 19:02</v>
+        <v>2026-08-29 16:44</v>
       </c>
       <c r="G124" t="str">
         <v>INGRESO</v>
@@ -7336,25 +7336,25 @@
         <v>5</v>
       </c>
       <c r="J124">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="K124" t="str">
-        <v>CM-20260823-00000378</v>
+        <v>CM-20260829-00000025</v>
       </c>
       <c r="L124" t="str">
         <v/>
       </c>
       <c r="M124" t="str">
-        <v>0132628_TA_Arunta</v>
+        <v>0134048_AQ_Punta_De_Bombon</v>
       </c>
       <c r="N124" t="str">
-        <v>N034-00000364</v>
+        <v>N020-00003521</v>
       </c>
       <c r="O124" t="str">
-        <v>SE RETIRO 5GL</v>
+        <v>Retira 5gl</v>
       </c>
       <c r="P124" t="str">
-        <v>TACNA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q124" t="str">
         <v>PROPIO</v>
@@ -7365,52 +7365,52 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B125" t="str">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C125" t="str">
-        <v>GL07COB</v>
+        <v>GL15COB</v>
       </c>
       <c r="D125" t="str">
-        <v>/api/evidencia/foto/7/107/comb_0.jpg?v=1788048995</v>
+        <v/>
       </c>
       <c r="E125" t="str">
-        <v>JOSE MIGUEL NINA ESQUIA</v>
+        <v>ELMER FLAVIANO CUBA ALVARADO</v>
       </c>
       <c r="F125" t="str">
-        <v>2026-08-24 19:07</v>
+        <v>2026-08-29 12:34</v>
       </c>
       <c r="G125" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H125" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I125" t="str">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="J125">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="K125" t="str">
-        <v>CM-20260823-00000378</v>
+        <v/>
       </c>
       <c r="L125" t="str">
-        <v>RFC-20260824-0029</v>
+        <v>se adjunta al termino de la faena</v>
       </c>
       <c r="M125" t="str">
-        <v>0132628_TA_Arunta</v>
+        <v>0133543_LH_Mapresa</v>
       </c>
       <c r="N125" t="str">
-        <v/>
+        <v>se adjunta al termino de la faena</v>
       </c>
       <c r="O125" t="str">
-        <v>N034-00000364 Se consume 5gl</v>
+        <v>Site: LH_DIVISORIA, LH_ALOMIAS, LH_MICROCUENCA TULUMAYO, LH_MAPRESA, LH_SAN JORGE</v>
       </c>
       <c r="P125" t="str">
-        <v>TACNA</v>
+        <v>HUANUCO-CERRO PASCO</v>
       </c>
       <c r="Q125" t="str">
         <v>PROPIO</v>
@@ -7421,22 +7421,22 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B126" t="str">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C126" t="str">
-        <v>GL11COB</v>
+        <v>GL07COB</v>
       </c>
       <c r="D126" t="str">
-        <v>/api/evidencia/foto/7/comb-1788039258843/comb_0.jpg?v=1788039262</v>
+        <v>/api/evidencia/foto/7/comb-1788048390431/comb_0.jpg?v=1788048393</v>
       </c>
       <c r="E126" t="str">
-        <v>DINO ANTHONY QUISPE FLORES</v>
+        <v>JOSE MIGUEL NINA ESQUIA</v>
       </c>
       <c r="F126" t="str">
-        <v>2026-08-29 16:33</v>
+        <v>2026-08-16 19:02</v>
       </c>
       <c r="G126" t="str">
         <v>INGRESO</v>
@@ -7445,28 +7445,28 @@
         <v>ygalvez</v>
       </c>
       <c r="I126" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J126">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K126" t="str">
-        <v>CM-20260829-00000147</v>
+        <v>CM-20260823-00000378</v>
       </c>
       <c r="L126" t="str">
         <v/>
       </c>
       <c r="M126" t="str">
-        <v>0132817_PN_Boris_Suas</v>
+        <v>0132628_TA_Arunta</v>
       </c>
       <c r="N126" t="str">
-        <v>N10-00000635</v>
+        <v>N034-00000364</v>
       </c>
       <c r="O126" t="str">
-        <v>Quispe Flores Dino usa qr de Chirinos 10gl</v>
+        <v>SE RETIRO 5GL</v>
       </c>
       <c r="P126" t="str">
-        <v>PUNO</v>
+        <v>TACNA</v>
       </c>
       <c r="Q126" t="str">
         <v>PROPIO</v>
@@ -7477,25 +7477,25 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B127" t="str">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C127" t="str">
-        <v>GL16COB</v>
+        <v>GL07COB</v>
       </c>
       <c r="D127" t="str">
-        <v>/api/evidencia/foto/7/comb-1788042722524/comb_0.jpg?v=1788042725</v>
+        <v>/api/evidencia/foto/7/107/comb_0.jpg?v=1788048995</v>
       </c>
       <c r="E127" t="str">
-        <v>MARCO ANTONIO SOTO BENIQUE</v>
+        <v>JOSE MIGUEL NINA ESQUIA</v>
       </c>
       <c r="F127" t="str">
-        <v>2026-08-20 17:29</v>
+        <v>2026-08-24 19:07</v>
       </c>
       <c r="G127" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H127" t="str">
         <v>ygalvez</v>
@@ -7504,25 +7504,25 @@
         <v>5</v>
       </c>
       <c r="J127">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K127" t="str">
-        <v>CM-20260826-00000222</v>
+        <v>CM-20260823-00000378</v>
       </c>
       <c r="L127" t="str">
-        <v/>
+        <v>RFC-20260824-0029</v>
       </c>
       <c r="M127" t="str">
-        <v>0132858_PN_Ananea</v>
+        <v>0132628_TA_Arunta</v>
       </c>
       <c r="N127" t="str">
-        <v>N015-00000913</v>
+        <v/>
       </c>
       <c r="O127" t="str">
-        <v>Retira 5gl</v>
+        <v>N034-00000364 Se consume 5gl</v>
       </c>
       <c r="P127" t="str">
-        <v>PUNO</v>
+        <v>TACNA</v>
       </c>
       <c r="Q127" t="str">
         <v>PROPIO</v>
@@ -7533,52 +7533,52 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="B128" t="str">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="C128" t="str">
-        <v>GL04COB</v>
+        <v>GL11COB</v>
       </c>
       <c r="D128" t="str">
-        <v>/api/evidencia/foto/7/comb-1788551594608/comb_0.jpg?v=1788551601</v>
+        <v>/api/evidencia/foto/7/comb-1788039258843/comb_0.jpg?v=1788039262</v>
       </c>
       <c r="E128" t="str">
-        <v>REYNER APAICO HURTADO</v>
+        <v>DINO ANTHONY QUISPE FLORES</v>
       </c>
       <c r="F128" t="str">
-        <v>2026-09-04 14:51</v>
+        <v>2026-08-29 16:33</v>
       </c>
       <c r="G128" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H128" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I128" t="str">
         <v>10</v>
       </c>
       <c r="J128">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K128" t="str">
-        <v>CM-20260903-00000238</v>
+        <v>CM-20260829-00000147</v>
       </c>
       <c r="L128" t="str">
-        <v>N007-00000393</v>
+        <v/>
       </c>
       <c r="M128" t="str">
-        <v>0134357_AY_Lecclespata</v>
+        <v>0132817_PN_Boris_Suas</v>
       </c>
       <c r="N128" t="str">
-        <v/>
+        <v>N10-00000635</v>
       </c>
       <c r="O128" t="str">
-        <v>N007-00000393</v>
+        <v>Quispe Flores Dino usa qr de Chirinos 10gl</v>
       </c>
       <c r="P128" t="str">
-        <v>AYACUCHO</v>
+        <v>PUNO</v>
       </c>
       <c r="Q128" t="str">
         <v>PROPIO</v>
@@ -7589,49 +7589,49 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B129" t="str">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C129" t="str">
-        <v>GL11COB</v>
+        <v>GL16COB</v>
       </c>
       <c r="D129" t="str">
-        <v>/api/evidencia/foto/7/comb-1788188269410/comb_0.jpg?v=1788188271</v>
+        <v>/api/evidencia/foto/7/comb-1788042722524/comb_0.jpg?v=1788042725</v>
       </c>
       <c r="E129" t="str">
         <v>MARCO ANTONIO SOTO BENIQUE</v>
       </c>
       <c r="F129" t="str">
-        <v>2026-08-27 09:54</v>
+        <v>2026-08-20 17:29</v>
       </c>
       <c r="G129" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H129" t="str">
         <v>ygalvez</v>
       </c>
       <c r="I129" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J129">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K129" t="str">
-        <v>CM-20260820-00000151</v>
+        <v>CM-20260826-00000222</v>
       </c>
       <c r="L129" t="str">
-        <v>RFC-20260827-0026</v>
+        <v/>
       </c>
       <c r="M129" t="str">
-        <v>0132860_PN_El_Dorado_Puno</v>
+        <v>0132858_PN_Ananea</v>
       </c>
       <c r="N129" t="str">
-        <v/>
+        <v>N015-00000913</v>
       </c>
       <c r="O129" t="str">
-        <v>N015-00000912 Se abastace 10gl tecnico Soto uso qr de Chirinos</v>
+        <v>Retira 5gl</v>
       </c>
       <c r="P129" t="str">
         <v>PUNO</v>
@@ -7645,52 +7645,52 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="B130" t="str">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="C130" t="str">
-        <v>GL16COB</v>
+        <v>GL04COB</v>
       </c>
       <c r="D130" t="str">
-        <v>/api/evidencia/foto/7/comb-1788042853980/comb_0.jpg?v=1788042857</v>
+        <v>/api/evidencia/foto/7/comb-1788551594608/comb_0.jpg?v=1788551601</v>
       </c>
       <c r="E130" t="str">
-        <v>MARCO ANTONIO SOTO BENIQUE</v>
+        <v>REYNER APAICO HURTADO</v>
       </c>
       <c r="F130" t="str">
-        <v>2026-08-27 17:32</v>
+        <v>2026-09-04 14:51</v>
       </c>
       <c r="G130" t="str">
         <v>GASTO</v>
       </c>
       <c r="H130" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I130" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J130">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K130" t="str">
-        <v>CM-20260826-00000222</v>
+        <v>CM-20260903-00000238</v>
       </c>
       <c r="L130" t="str">
-        <v>RFC-20260827-0019</v>
+        <v>N007-00000393</v>
       </c>
       <c r="M130" t="str">
-        <v>0132858_PN_Ananea</v>
+        <v>0134357_AY_Lecclespata</v>
       </c>
       <c r="N130" t="str">
         <v/>
       </c>
       <c r="O130" t="str">
-        <v>N015-00000913</v>
+        <v>N007-00000393</v>
       </c>
       <c r="P130" t="str">
-        <v>PUNO</v>
+        <v>AYACUCHO</v>
       </c>
       <c r="Q130" t="str">
         <v>PROPIO</v>
@@ -7701,22 +7701,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B131" t="str">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C131" t="str">
         <v>GL11COB</v>
       </c>
       <c r="D131" t="str">
-        <v>/api/evidencia/foto/7/comb-1788043322013/comb_0.jpg?v=1788043324</v>
+        <v>/api/evidencia/foto/7/comb-1788188269410/comb_0.jpg?v=1788188271</v>
       </c>
       <c r="E131" t="str">
-        <v>DINO ANTHONY QUISPE FLORES</v>
+        <v>MARCO ANTONIO SOTO BENIQUE</v>
       </c>
       <c r="F131" t="str">
-        <v>2026-08-29 17:38</v>
+        <v>2026-08-27 09:54</v>
       </c>
       <c r="G131" t="str">
         <v>GASTO</v>
@@ -7725,25 +7725,25 @@
         <v>ygalvez</v>
       </c>
       <c r="I131" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J131">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K131" t="str">
-        <v>CM-20260829-00000147</v>
+        <v>CM-20260820-00000151</v>
       </c>
       <c r="L131" t="str">
-        <v>RFC-20260829-0016</v>
+        <v>RFC-20260827-0026</v>
       </c>
       <c r="M131" t="str">
-        <v>0132817_PN_Boris_Suas</v>
+        <v>0132860_PN_El_Dorado_Puno</v>
       </c>
       <c r="N131" t="str">
         <v/>
       </c>
       <c r="O131" t="str">
-        <v>N010-00000635 RETIRA 10 SOLO USA 5</v>
+        <v>N015-00000912 Se abastace 10gl tecnico Soto uso qr de Chirinos</v>
       </c>
       <c r="P131" t="str">
         <v>PUNO</v>
@@ -7757,49 +7757,49 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B132" t="str">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C132" t="str">
         <v>GL16COB</v>
       </c>
       <c r="D132" t="str">
-        <v>/api/evidencia/foto/7/comb-1788188691571/comb_0.jpg?v=1788188693</v>
+        <v>/api/evidencia/foto/7/comb-1788042853980/comb_0.jpg?v=1788042857</v>
       </c>
       <c r="E132" t="str">
         <v>MARCO ANTONIO SOTO BENIQUE</v>
       </c>
       <c r="F132" t="str">
-        <v>2026-08-30 10:00</v>
+        <v>2026-08-27 17:32</v>
       </c>
       <c r="G132" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H132" t="str">
         <v>ygalvez</v>
       </c>
       <c r="I132" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J132">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K132" t="str">
-        <v>CM-20260830-00000074</v>
+        <v>CM-20260826-00000222</v>
       </c>
       <c r="L132" t="str">
-        <v/>
+        <v>RFC-20260827-0019</v>
       </c>
       <c r="M132" t="str">
-        <v>0132801_PN_Jayllihuaya</v>
+        <v>0132858_PN_Ananea</v>
       </c>
       <c r="N132" t="str">
-        <v>N005-00001034</v>
+        <v/>
       </c>
       <c r="O132" t="str">
-        <v>N005-00001034 Se retira 10gl</v>
+        <v>N015-00000913</v>
       </c>
       <c r="P132" t="str">
         <v>PUNO</v>
@@ -7813,52 +7813,52 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="B133" t="str">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C133" t="str">
-        <v>GL23COB</v>
+        <v>GL11COB</v>
       </c>
       <c r="D133" t="str">
-        <v>/api/evidencia/foto/7/26/comb_0.jpg?v=1787344353</v>
+        <v>/api/evidencia/foto/7/comb-1788043322013/comb_0.jpg?v=1788043324</v>
       </c>
       <c r="E133" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>DINO ANTHONY QUISPE FLORES</v>
       </c>
       <c r="F133" t="str">
-        <v>2026-08-21 00:00</v>
+        <v>2026-08-29 17:38</v>
       </c>
       <c r="G133" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H133" t="str">
         <v>ygalvez</v>
       </c>
       <c r="I133" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J133">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K133" t="str">
-        <v>CM-20260819-00000056</v>
+        <v>CM-20260829-00000147</v>
       </c>
       <c r="L133" t="str">
-        <v/>
+        <v>RFC-20260829-0016</v>
       </c>
       <c r="M133" t="str">
-        <v/>
+        <v>0132817_PN_Boris_Suas</v>
       </c>
       <c r="N133" t="str">
-        <v>N029-00001191</v>
+        <v/>
       </c>
       <c r="O133" t="str">
-        <v>0134389EL_CARMEN_AQP</v>
+        <v>N010-00000635 RETIRA 10 SOLO USA 5</v>
       </c>
       <c r="P133" t="str">
-        <v>AREQUIPA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q133" t="str">
         <v>PROPIO</v>
@@ -7869,52 +7869,52 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B134" t="str">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C134" t="str">
-        <v>GL02COB</v>
+        <v>GL16COB</v>
       </c>
       <c r="D134" t="str">
-        <v>/api/evidencia/foto/7/comb-1788195564512/comb_0.jpg?v=1788195565</v>
+        <v>/api/evidencia/foto/7/comb-1788188691571/comb_0.jpg?v=1788188693</v>
       </c>
       <c r="E134" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MARCO ANTONIO SOTO BENIQUE</v>
       </c>
       <c r="F134" t="str">
-        <v>2026-08-29 16:40</v>
+        <v>2026-08-30 10:00</v>
       </c>
       <c r="G134" t="str">
         <v>INGRESO</v>
       </c>
       <c r="H134" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I134" t="str">
         <v>10</v>
       </c>
       <c r="J134">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K134" t="str">
-        <v>CM -20260829-00000043</v>
+        <v>CM-20260830-00000074</v>
       </c>
       <c r="L134" t="str">
-        <v>N014-00001570</v>
+        <v/>
       </c>
       <c r="M134" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v>0132801_PN_Jayllihuaya</v>
       </c>
       <c r="N134" t="str">
-        <v>RFC-20260829-0013</v>
+        <v>N005-00001034</v>
       </c>
       <c r="O134" t="str">
-        <v>SE INGRESO EL CONSUMO DE 10 GALONES</v>
+        <v>N005-00001034 Se retira 10gl</v>
       </c>
       <c r="P134" t="str">
-        <v>CHINCHA</v>
+        <v>PUNO</v>
       </c>
       <c r="Q134" t="str">
         <v>PROPIO</v>
@@ -7925,52 +7925,52 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="B135" t="str">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="C135" t="str">
-        <v>GL02COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D135" t="str">
-        <v>/api/evidencia/foto/7/comb-1788196031461/comb_0.jpg?v=1788196033</v>
+        <v>/api/evidencia/foto/7/26/comb_0.jpg?v=1787344353</v>
       </c>
       <c r="E135" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F135" t="str">
-        <v>2026-08-29 16:04</v>
+        <v>2026-08-21 00:00</v>
       </c>
       <c r="G135" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H135" t="str">
-        <v>rllanos</v>
+        <v>ygalvez</v>
       </c>
       <c r="I135" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J135">
-        <v>-10</v>
+        <v>6</v>
       </c>
       <c r="K135" t="str">
-        <v>CM -20260829-00000043</v>
+        <v>CM-20260819-00000056</v>
       </c>
       <c r="L135" t="str">
-        <v>CM-20260829-00000043</v>
+        <v/>
       </c>
       <c r="M135" t="str">
-        <v>0133243_IC_Bodega_COW</v>
+        <v/>
       </c>
       <c r="N135" t="str">
-        <v/>
+        <v>N029-00001191</v>
       </c>
       <c r="O135" t="str">
-        <v>SE CONSUMIO LOS 10 GALONES RECIBO N14-00001570</v>
+        <v>0134389EL_CARMEN_AQP</v>
       </c>
       <c r="P135" t="str">
-        <v>CHINCHA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q135" t="str">
         <v>PROPIO</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B136" t="str">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C136" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D136" t="str">
-        <v>/api/evidencia/foto/7/comb-1788196696307/comb_0.jpg?v=1788196697</v>
+        <v>/api/evidencia/foto/7/comb-1788195564512/comb_0.jpg?v=1788195565</v>
       </c>
       <c r="E136" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F136" t="str">
-        <v>2026-08-30 19:24</v>
+        <v>2026-08-29 16:40</v>
       </c>
       <c r="G136" t="str">
         <v>INGRESO</v>
@@ -8011,19 +8011,19 @@
         <v>10</v>
       </c>
       <c r="K136" t="str">
-        <v>CM -20260829-00000043</v>
+        <v/>
       </c>
       <c r="L136" t="str">
-        <v>N014-00001572</v>
+        <v>N014-00001570</v>
       </c>
       <c r="M136" t="str">
         <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N136" t="str">
-        <v>RFC-20260829-0014</v>
+        <v>RFC-20260829-0013</v>
       </c>
       <c r="O136" t="str">
-        <v>SE INGRESO 10  GALOES PARA CONSUMO</v>
+        <v>SE INGRESO EL CONSUMO DE 10 GALONES</v>
       </c>
       <c r="P136" t="str">
         <v>CHINCHA</v>
@@ -8032,27 +8032,27 @@
         <v>PROPIO</v>
       </c>
       <c r="R136" t="str">
-        <v/>
+        <v>hvargas</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B137" t="str">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C137" t="str">
         <v>GL02COB</v>
       </c>
       <c r="D137" t="str">
-        <v>/api/evidencia/foto/7/comb-1788197041617/comb_0.jpg?v=1788197043</v>
+        <v>/api/evidencia/foto/7/comb-1788196031461/comb_0.jpg?v=1788196033</v>
       </c>
       <c r="E137" t="str">
         <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F137" t="str">
-        <v>2026-08-31 07:22</v>
+        <v>2026-08-29 16:04</v>
       </c>
       <c r="G137" t="str">
         <v>GASTO</v>
@@ -8067,10 +8067,10 @@
         <v>0</v>
       </c>
       <c r="K137" t="str">
-        <v>CM -20260829-00000043</v>
+        <v>CM-20260829-00000043</v>
       </c>
       <c r="L137" t="str">
-        <v>RFC-20260829-0014</v>
+        <v>CM-20260829-00000043</v>
       </c>
       <c r="M137" t="str">
         <v>0133243_IC_Bodega_COW</v>
@@ -8079,7 +8079,7 @@
         <v/>
       </c>
       <c r="O137" t="str">
-        <v>SE CONSUMIO LOS 10 GALONES  N14-00001572</v>
+        <v>SE CONSUMIO LOS 10 GALONES RECIBO N14-00001570</v>
       </c>
       <c r="P137" t="str">
         <v>CHINCHA</v>
@@ -8088,57 +8088,57 @@
         <v>PROPIO</v>
       </c>
       <c r="R137" t="str">
-        <v/>
+        <v>hvargas</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B138" t="str">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C138" t="str">
-        <v>GL23COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D138" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1788196696307/comb_0.jpg?v=1788196697</v>
       </c>
       <c r="E138" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F138" t="str">
-        <v>2026-08-29 21:22</v>
+        <v>2026-08-30 19:24</v>
       </c>
       <c r="G138" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H138" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I138" t="str">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="J138">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K138" t="str">
-        <v>CM-20260829-00000025</v>
+        <v>CM -20260829-00000043</v>
       </c>
       <c r="L138" t="str">
-        <v>RFC-20260829-0022</v>
+        <v>N014-00001572</v>
       </c>
       <c r="M138" t="str">
-        <v>0134048_AQ_Punta_De_Bombon</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N138" t="str">
-        <v/>
+        <v>RFC-20260829-0014</v>
       </c>
       <c r="O138" t="str">
-        <v>N025-00006024 Se uso 2.5gl</v>
+        <v>SE INGRESO 10  GALOES PARA CONSUMO</v>
       </c>
       <c r="P138" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q138" t="str">
         <v>PROPIO</v>
@@ -8149,108 +8149,108 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B139" t="str">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C139" t="str">
-        <v>GL23COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D139" t="str">
-        <v>/api/evidencia/foto/7/comb-1788057022800/comb_0.jpg?v=1788057025</v>
+        <v>/api/evidencia/foto/7/comb-1788197041617/comb_0.jpg?v=1788197043</v>
       </c>
       <c r="E139" t="str">
-        <v>MIGUEL TONY CACYALLA HUAMANI</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F139" t="str">
-        <v>2026-08-29 21:29</v>
+        <v>2026-08-31 07:22</v>
       </c>
       <c r="G139" t="str">
         <v>GASTO</v>
       </c>
       <c r="H139" t="str">
-        <v>ygalvez</v>
+        <v>rllanos</v>
       </c>
       <c r="I139" t="str">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="J139">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="K139" t="str">
-        <v>CM-20260829-00000025</v>
+        <v>CM -20260829-00000043</v>
       </c>
       <c r="L139" t="str">
-        <v>RFC-20260829-0026</v>
+        <v>RFC-20260829-0014</v>
       </c>
       <c r="M139" t="str">
-        <v>0134048_AQ_Punta_De_Bombon</v>
+        <v>0133243_IC_Bodega_COW</v>
       </c>
       <c r="N139" t="str">
         <v/>
       </c>
       <c r="O139" t="str">
-        <v>N020-00003521 se uso 5gl</v>
+        <v>SE CONSUMIO LOS 10 GALONES  N14-00001572</v>
       </c>
       <c r="P139" t="str">
-        <v>AREQUIPA</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q139" t="str">
         <v>PROPIO</v>
       </c>
       <c r="R139" t="str">
-        <v>hvargas</v>
+        <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B140" t="str">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C140" t="str">
-        <v>GL24COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D140" t="str">
-        <v>/api/evidencia/foto/7/comb-1788057792165/comb_0.jpg?v=1788057796</v>
+        <v/>
       </c>
       <c r="E140" t="str">
-        <v>YOVANIE ENRIQUEZ CASTILLO</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F140" t="str">
-        <v>2026-08-21 21:41</v>
+        <v>2026-08-29 21:22</v>
       </c>
       <c r="G140" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H140" t="str">
         <v>ygalvez</v>
       </c>
       <c r="I140" t="str">
-        <v>9.95</v>
+        <v>2.5</v>
       </c>
       <c r="J140">
-        <v>9.95</v>
+        <v>5</v>
       </c>
       <c r="K140" t="str">
-        <v>CM-20260828-00000047</v>
+        <v>CM-20260829-00000025</v>
       </c>
       <c r="L140" t="str">
-        <v/>
+        <v>RFC-20260829-0022</v>
       </c>
       <c r="M140" t="str">
-        <v>0131349_CS_Aero_Cusco</v>
+        <v>0134048_AQ_Punta_De_Bombon</v>
       </c>
       <c r="N140" t="str">
-        <v>N574-00038015</v>
+        <v/>
       </c>
       <c r="O140" t="str">
-        <v>N574-00038015 RETIRO 9.95</v>
+        <v>N025-00006024 Se uso 2.5gl</v>
       </c>
       <c r="P140" t="str">
-        <v>CUZCO</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q140" t="str">
         <v>PROPIO</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B141" t="str">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C141" t="str">
-        <v>GL24COB</v>
+        <v>GL23COB</v>
       </c>
       <c r="D141" t="str">
-        <v>/api/evidencia/foto/7/comb-1788057951462/comb_0.jpg?v=1788057954</v>
+        <v>/api/evidencia/foto/7/comb-1788057022800/comb_0.jpg?v=1788057025</v>
       </c>
       <c r="E141" t="str">
-        <v>YOVANIE ENRIQUEZ CASTILLO</v>
+        <v>MIGUEL TONY CACYALLA HUAMANI</v>
       </c>
       <c r="F141" t="str">
-        <v>2026-08-29 21:44</v>
+        <v>2026-08-29 21:29</v>
       </c>
       <c r="G141" t="str">
         <v>GASTO</v>
@@ -8285,54 +8285,54 @@
         <v>ygalvez</v>
       </c>
       <c r="I141" t="str">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J141">
-        <v>6.95</v>
+        <v>3.2</v>
       </c>
       <c r="K141" t="str">
-        <v>CM-20260828-00000047</v>
+        <v>CM-20260829-00000025</v>
       </c>
       <c r="L141" t="str">
-        <v>RFC-20260828-0005</v>
+        <v>RFC-20260829-0026</v>
       </c>
       <c r="M141" t="str">
-        <v>0131349_CS_Aero_Cusco</v>
+        <v>0134048_AQ_Punta_De_Bombon</v>
       </c>
       <c r="N141" t="str">
         <v/>
       </c>
       <c r="O141" t="str">
-        <v>N574-00038015 RETIRO 3GL</v>
+        <v>N020-00003521 se uso 5gl</v>
       </c>
       <c r="P141" t="str">
-        <v>CUZCO</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q141" t="str">
         <v>PROPIO</v>
       </c>
       <c r="R141" t="str">
-        <v/>
+        <v>hvargas</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="B142" t="str">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="C142" t="str">
-        <v>GL17COB</v>
+        <v>GL24COB</v>
       </c>
       <c r="D142" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1788057792165/comb_0.jpg?v=1788057796</v>
       </c>
       <c r="E142" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>YOVANIE ENRIQUEZ CASTILLO</v>
       </c>
       <c r="F142" t="str">
-        <v>2026-08-20 00:00</v>
+        <v>2026-08-21 21:41</v>
       </c>
       <c r="G142" t="str">
         <v>INGRESO</v>
@@ -8341,28 +8341,28 @@
         <v>ygalvez</v>
       </c>
       <c r="I142" t="str">
-        <v>10</v>
+        <v>9.95</v>
       </c>
       <c r="J142">
-        <v>10</v>
+        <v>19.2</v>
       </c>
       <c r="K142" t="str">
-        <v>CM-20260820-00000089</v>
+        <v>CM-20260828-00000047</v>
       </c>
       <c r="L142" t="str">
         <v/>
       </c>
       <c r="M142" t="str">
-        <v/>
+        <v>0131349_CS_Aero_Cusco</v>
       </c>
       <c r="N142" t="str">
-        <v/>
+        <v>N574-00038015</v>
       </c>
       <c r="O142" t="str">
-        <v>0134048_AQ_Punta_De_Bombon</v>
+        <v>N574-00038015 RETIRO 9.95</v>
       </c>
       <c r="P142" t="str">
-        <v>AREQUIPA</v>
+        <v>CUZCO</v>
       </c>
       <c r="Q142" t="str">
         <v>PROPIO</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="B143" t="str">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="C143" t="str">
-        <v>GL17COB</v>
+        <v>GL24COB</v>
       </c>
       <c r="D143" t="str">
-        <v>/api/evidencia/foto/7/comb-1787604529515/comb_0.jpg?v=1787604530</v>
+        <v>/api/evidencia/foto/7/comb-1788057951462/comb_0.jpg?v=1788057954</v>
       </c>
       <c r="E143" t="str">
-        <v>MANUEL JOEL CCARI MAMANI</v>
+        <v>YOVANIE ENRIQUEZ CASTILLO</v>
       </c>
       <c r="F143" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-29 21:44</v>
       </c>
       <c r="G143" t="str">
         <v>GASTO</v>
@@ -8397,28 +8397,28 @@
         <v>ygalvez</v>
       </c>
       <c r="I143" t="str">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J143">
-        <v>10</v>
+        <v>6.95</v>
       </c>
       <c r="K143" t="str">
-        <v>CM-20260823-00000152</v>
+        <v>CM-20260828-00000047</v>
       </c>
       <c r="L143" t="str">
-        <v>RFC-20260823-0020</v>
+        <v>RFC-20260828-0005</v>
       </c>
       <c r="M143" t="str">
-        <v/>
+        <v>0131349_CS_Aero_Cusco</v>
       </c>
       <c r="N143" t="str">
-        <v>N030-00001214</v>
+        <v/>
       </c>
       <c r="O143" t="str">
-        <v>0130929_AQ_Cocachacra N030-00001214 10GL</v>
+        <v>N574-00038015 RETIRO 3GL</v>
       </c>
       <c r="P143" t="str">
-        <v>AREQUIPA</v>
+        <v>CUZCO</v>
       </c>
       <c r="Q143" t="str">
         <v>PROPIO</v>
@@ -8429,52 +8429,52 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B144" t="str">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C144" t="str">
-        <v>GL09COB</v>
+        <v>GL17COB</v>
       </c>
       <c r="D144" t="str">
-        <v>/api/evidencia/foto/7/comb-1787605570128/comb_0.jpg?v=1787605171</v>
+        <v/>
       </c>
       <c r="E144" t="str">
-        <v>BRIAN JESUS CABRERA ASCENCIO</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F144" t="str">
-        <v>2026-08-24 00:00</v>
+        <v>2026-08-20 00:00</v>
       </c>
       <c r="G144" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H144" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I144" t="str">
         <v>10</v>
       </c>
       <c r="J144">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K144" t="str">
-        <v>CM-20260823-00000101</v>
+        <v>CM-20260820-00000089</v>
       </c>
       <c r="L144" t="str">
-        <v>N016-00002175 0132282_IC_Jose_Miranda // N016-00002175</v>
+        <v/>
       </c>
       <c r="M144" t="str">
         <v/>
       </c>
       <c r="N144" t="str">
-        <v>N016-00002175</v>
+        <v/>
       </c>
       <c r="O144" t="str">
-        <v>ATENCION DE 10GLS CORTE PROGRAMADO</v>
+        <v>0134048_AQ_Punta_De_Bombon</v>
       </c>
       <c r="P144" t="str">
-        <v>ICA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q144" t="str">
         <v>PROPIO</v>
@@ -8485,19 +8485,19 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B145" t="str">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C145" t="str">
-        <v>GL09COB</v>
+        <v>GL17COB</v>
       </c>
       <c r="D145" t="str">
-        <v>/api/evidencia/foto/7/comb-1787605914145/comb_0.jpg?v=1787605515</v>
+        <v>/api/evidencia/foto/7/comb-1787604529515/comb_0.jpg?v=1787604530</v>
       </c>
       <c r="E145" t="str">
-        <v>BRIAN JESUS CABRERA ASCENCIO</v>
+        <v>MANUEL JOEL CCARI MAMANI</v>
       </c>
       <c r="F145" t="str">
         <v>2026-08-24 00:00</v>
@@ -8506,7 +8506,7 @@
         <v>GASTO</v>
       </c>
       <c r="H145" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I145" t="str">
         <v>10</v>
@@ -8515,22 +8515,22 @@
         <v>10</v>
       </c>
       <c r="K145" t="str">
-        <v>CM-20260823-00000126</v>
+        <v>CM-20260823-00000152</v>
       </c>
       <c r="L145" t="str">
-        <v>N016-00002175/ 0134681_IC_Clavelles</v>
+        <v>RFC-20260823-0020</v>
       </c>
       <c r="M145" t="str">
-        <v>N016-00002175</v>
+        <v/>
       </c>
       <c r="N145" t="str">
-        <v>N016-00002175</v>
+        <v>N030-00001214</v>
       </c>
       <c r="O145" t="str">
-        <v>N016-00002175/ 0134681_IC_Clavelles</v>
+        <v>0130929_AQ_Cocachacra N030-00001214 10GL</v>
       </c>
       <c r="P145" t="str">
-        <v>ICA</v>
+        <v>AREQUIPA</v>
       </c>
       <c r="Q145" t="str">
         <v>PROPIO</v>
@@ -8541,52 +8541,52 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B146" t="str">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C146" t="str">
-        <v>GL19COB</v>
+        <v>GL09COB</v>
       </c>
       <c r="D146" t="str">
-        <v>/api/evidencia/foto/7/comb-1787667548758/comb_0.jpg?v=1787667550</v>
+        <v>/api/evidencia/foto/7/comb-1787605570128/comb_0.jpg?v=1787605171</v>
       </c>
       <c r="E146" t="str">
-        <v>MOISES ANGEL AYÑAYANQUI RIOS</v>
+        <v>BRIAN JESUS CABRERA ASCENCIO</v>
       </c>
       <c r="F146" t="str">
         <v>2026-08-24 00:00</v>
       </c>
       <c r="G146" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H146" t="str">
-        <v>ygalvez</v>
+        <v>lgutierrez</v>
       </c>
       <c r="I146" t="str">
         <v>10</v>
       </c>
       <c r="J146">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K146" t="str">
-        <v>CM-20260825-00000083</v>
+        <v>CM-20260823-00000101</v>
       </c>
       <c r="L146" t="str">
-        <v/>
+        <v>N016-00002175 0132282_IC_Jose_Miranda // N016-00002175</v>
       </c>
       <c r="M146" t="str">
         <v/>
       </c>
       <c r="N146" t="str">
-        <v>N331-00031308</v>
+        <v>N016-00002175</v>
       </c>
       <c r="O146" t="str">
-        <v>0130931_AQ_CHALA  N331-00031308 10gl</v>
+        <v>ATENCION DE 10GLS CORTE PROGRAMADO</v>
       </c>
       <c r="P146" t="str">
-        <v>CAMANA</v>
+        <v>ICA</v>
       </c>
       <c r="Q146" t="str">
         <v>PROPIO</v>
@@ -8597,19 +8597,19 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B147" t="str">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C147" t="str">
-        <v>GL02COB</v>
+        <v>GL09COB</v>
       </c>
       <c r="D147" t="str">
-        <v>/api/evidencia/foto/7/comb-1787700742035/comb_0.jpg?v=1787700342</v>
+        <v>/api/evidencia/foto/7/comb-1787605914145/comb_0.jpg?v=1787605515</v>
       </c>
       <c r="E147" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>BRIAN JESUS CABRERA ASCENCIO</v>
       </c>
       <c r="F147" t="str">
         <v>2026-08-24 00:00</v>
@@ -8621,28 +8621,28 @@
         <v>lgutierrez</v>
       </c>
       <c r="I147" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J147">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K147" t="str">
-        <v>CM-20260823-00000121</v>
+        <v>CM-20260823-00000126</v>
       </c>
       <c r="L147" t="str">
-        <v>N014 - 00001524</v>
+        <v>N016-00002175/ 0134681_IC_Clavelles</v>
       </c>
       <c r="M147" t="str">
-        <v>CORTE PROGRAMADO SITE 013210702_IC_Idelfonso_Lira</v>
+        <v>N016-00002175</v>
       </c>
       <c r="N147" t="str">
-        <v>N014 - 00001524</v>
+        <v>N016-00002175</v>
       </c>
       <c r="O147" t="str">
-        <v>CORTE PROGRAMADO SITE 013210702_IC_Idelfonso_Lira</v>
+        <v>N016-00002175/ 0134681_IC_Clavelles</v>
       </c>
       <c r="P147" t="str">
-        <v>CHINCHA</v>
+        <v>ICA</v>
       </c>
       <c r="Q147" t="str">
         <v>PROPIO</v>
@@ -8653,52 +8653,52 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B148" t="str">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C148" t="str">
-        <v>GL02COB</v>
+        <v>GL19COB</v>
       </c>
       <c r="D148" t="str">
-        <v>/api/evidencia/foto/7/comb-1787701180909/comb_0.jpg?v=1787700780</v>
+        <v>/api/evidencia/foto/7/comb-1787667548758/comb_0.jpg?v=1787667550</v>
       </c>
       <c r="E148" t="str">
-        <v>LUIS ANGEL PADILLA PORTILLA</v>
+        <v>MOISES ANGEL AYÑAYANQUI RIOS</v>
       </c>
       <c r="F148" t="str">
         <v>2026-08-24 00:00</v>
       </c>
       <c r="G148" t="str">
-        <v>GASTO</v>
+        <v>INGRESO</v>
       </c>
       <c r="H148" t="str">
-        <v>lgutierrez</v>
+        <v>ygalvez</v>
       </c>
       <c r="I148" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J148">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K148" t="str">
-        <v>CM-20260810-00000114</v>
+        <v>CM-20260825-00000083</v>
       </c>
       <c r="L148" t="str">
-        <v>N014 - 00001524</v>
+        <v/>
       </c>
       <c r="M148" t="str">
-        <v>SITE 0132254_IC_Garzas_Mir_1900</v>
+        <v/>
       </c>
       <c r="N148" t="str">
-        <v>N014 - 00001524</v>
+        <v>N331-00031308</v>
       </c>
       <c r="O148" t="str">
-        <v>CORTE PROGRAMADO SITE 0132254_IC_Garzas_Mir_1900</v>
+        <v>0130931_AQ_CHALA  N331-00031308 10gl</v>
       </c>
       <c r="P148" t="str">
-        <v>CHINCHA</v>
+        <v>CAMANA</v>
       </c>
       <c r="Q148" t="str">
         <v>PROPIO</v>
@@ -8709,52 +8709,52 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B149" t="str">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C149" t="str">
-        <v>GL08COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D149" t="str">
-        <v/>
+        <v>/api/evidencia/foto/7/comb-1787700742035/comb_0.jpg?v=1787700342</v>
       </c>
       <c r="E149" t="str">
-        <v>MARCO ALBERTO BENDEZU MORALES</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F149" t="str">
-        <v>2026-08-25 00:00</v>
+        <v>2026-08-24 00:00</v>
       </c>
       <c r="G149" t="str">
-        <v>INGRESO</v>
+        <v>GASTO</v>
       </c>
       <c r="H149" t="str">
         <v>lgutierrez</v>
       </c>
       <c r="I149" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J149">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K149" t="str">
-        <v>CM-20260825-00000172</v>
+        <v>CM-20260823-00000121</v>
       </c>
       <c r="L149" t="str">
-        <v/>
+        <v>N014 - 00001524</v>
       </c>
       <c r="M149" t="str">
-        <v/>
+        <v>CORTE PROGRAMADO SITE 013210702_IC_Idelfonso_Lira</v>
       </c>
       <c r="N149" t="str">
-        <v>SE MEITE DESPUES</v>
+        <v>N014 - 00001524</v>
       </c>
       <c r="O149" t="str">
-        <v>SE DIO CAJA CHICA JESSICA</v>
+        <v>CORTE PROGRAMADO SITE 013210702_IC_Idelfonso_Lira</v>
       </c>
       <c r="P149" t="str">
-        <v>LA MERCED</v>
+        <v>CHINCHA</v>
       </c>
       <c r="Q149" t="str">
         <v>PROPIO</v>
@@ -8765,19 +8765,19 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B150" t="str">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C150" t="str">
-        <v>GL18COB</v>
+        <v>GL02COB</v>
       </c>
       <c r="D150" t="str">
-        <v>/api/evidencia/foto/7/comb-1787698885596/comb_0.jpg?v=1787698486</v>
+        <v>/api/evidencia/foto/7/comb-1787701180909/comb_0.jpg?v=1787700780</v>
       </c>
       <c r="E150" t="str">
-        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+        <v>LUIS ANGEL PADILLA PORTILLA</v>
       </c>
       <c r="F150" t="str">
         <v>2026-08-24 00:00</v>
@@ -8792,36 +8792,148 @@
         <v>5</v>
       </c>
       <c r="J150">
+        <v>10</v>
+      </c>
+      <c r="K150" t="str">
+        <v>CM-20260810-00000114</v>
+      </c>
+      <c r="L150" t="str">
+        <v>N014 - 00001524</v>
+      </c>
+      <c r="M150" t="str">
+        <v>SITE 0132254_IC_Garzas_Mir_1900</v>
+      </c>
+      <c r="N150" t="str">
+        <v>N014 - 00001524</v>
+      </c>
+      <c r="O150" t="str">
+        <v>CORTE PROGRAMADO SITE 0132254_IC_Garzas_Mir_1900</v>
+      </c>
+      <c r="P150" t="str">
+        <v>CHINCHA</v>
+      </c>
+      <c r="Q150" t="str">
+        <v>PROPIO</v>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>63</v>
+      </c>
+      <c r="B151" t="str">
+        <v>63</v>
+      </c>
+      <c r="C151" t="str">
+        <v>GL08COB</v>
+      </c>
+      <c r="D151" t="str">
+        <v/>
+      </c>
+      <c r="E151" t="str">
+        <v>MARCO ALBERTO BENDEZU MORALES</v>
+      </c>
+      <c r="F151" t="str">
+        <v>2026-08-25 00:00</v>
+      </c>
+      <c r="G151" t="str">
+        <v>INGRESO</v>
+      </c>
+      <c r="H151" t="str">
+        <v>lgutierrez</v>
+      </c>
+      <c r="I151" t="str">
+        <v>10</v>
+      </c>
+      <c r="J151">
+        <v>10</v>
+      </c>
+      <c r="K151" t="str">
+        <v>CM-20260825-00000172</v>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v>SE MEITE DESPUES</v>
+      </c>
+      <c r="O151" t="str">
+        <v>SE DIO CAJA CHICA JESSICA</v>
+      </c>
+      <c r="P151" t="str">
+        <v>LA MERCED</v>
+      </c>
+      <c r="Q151" t="str">
+        <v>PROPIO</v>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>54</v>
+      </c>
+      <c r="B152" t="str">
+        <v>65</v>
+      </c>
+      <c r="C152" t="str">
+        <v>GL18COB</v>
+      </c>
+      <c r="D152" t="str">
+        <v>/api/evidencia/foto/7/comb-1787698885596/comb_0.jpg?v=1787698486</v>
+      </c>
+      <c r="E152" t="str">
+        <v>EDDY GABRIEL GARCIA BRICEÑO</v>
+      </c>
+      <c r="F152" t="str">
+        <v>2026-08-24 00:00</v>
+      </c>
+      <c r="G152" t="str">
+        <v>GASTO</v>
+      </c>
+      <c r="H152" t="str">
+        <v>lgutierrez</v>
+      </c>
+      <c r="I152" t="str">
         <v>5</v>
       </c>
-      <c r="K150" t="str">
+      <c r="J152">
+        <v>5</v>
+      </c>
+      <c r="K152" t="str">
         <v>CM-20260823-00000257</v>
       </c>
-      <c r="L150" t="str">
-        <v/>
-      </c>
-      <c r="M150" t="str">
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
         <v>CORTE PROGRAMADO  SITE 0134676_IC_Calle_Osores REALIZADO X YAIR ESCAKJADILLO</v>
       </c>
-      <c r="N150" t="str">
+      <c r="N152" t="str">
         <v>N024-00002841</v>
       </c>
-      <c r="O150" t="str">
+      <c r="O152" t="str">
         <v>CORTE PROGRAMADO  SITE 0134676_IC_Calle_Osores</v>
       </c>
-      <c r="P150" t="str">
+      <c r="P152" t="str">
         <v>ICA</v>
       </c>
-      <c r="Q150" t="str">
-        <v>PROPIO</v>
-      </c>
-      <c r="R150" t="str">
+      <c r="Q152" t="str">
+        <v>PROPIO</v>
+      </c>
+      <c r="R152" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R152"/>
   </ignoredErrors>
 </worksheet>
 </file>